--- a/data/personalia/8 SB.xlsx
+++ b/data/personalia/8 SB.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\OneDrive\Desktop\p3ste-app\Fix\Personalia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\18. STE APP\Personalia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70406EE-3DDC-4091-AB1C-668F073A98A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C62FD6D6-11BD-4734-98A1-38AE2AE8DBC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,10 +17,19 @@
     <sheet name="LIST_DATA" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$199</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -29,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="404">
   <si>
     <t>Wilayah</t>
   </si>
@@ -163,97 +172,244 @@
     <t>Kaur UPT Workshop</t>
   </si>
   <si>
+    <t>WS LAA Mri</t>
+  </si>
+  <si>
+    <t>LAA 1.4 Thb</t>
+  </si>
+  <si>
+    <t>Teknisi</t>
+  </si>
+  <si>
+    <t>LAA 1.1 Rk</t>
+  </si>
+  <si>
+    <t>LAA 1.14 Nmo</t>
+  </si>
+  <si>
+    <t>LAA 1.2 Prp</t>
+  </si>
+  <si>
+    <t>LAA 1.3 Srp</t>
+  </si>
+  <si>
+    <t>LAA 1.5 Du</t>
+  </si>
+  <si>
+    <t>LAA 1.11 Psm</t>
+  </si>
+  <si>
+    <t>LAA 1.6 Jakk</t>
+  </si>
+  <si>
+    <t>LAA 1.7 Pse</t>
+  </si>
+  <si>
+    <t>LAA 1.8 Mri</t>
+  </si>
+  <si>
+    <t>LAA 1.9 Jng</t>
+  </si>
+  <si>
+    <t>LAA 1.10 Ckr</t>
+  </si>
+  <si>
+    <t>LAA 1.12 Dp</t>
+  </si>
+  <si>
+    <t>LAA 1.13 Boo</t>
+  </si>
+  <si>
+    <t>LAA 1.15 Bst</t>
+  </si>
+  <si>
+    <t>PMP Lanjutan</t>
+  </si>
+  <si>
+    <t>PMP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Lanjutan</t>
+  </si>
+  <si>
+    <t>Calon Pekerja</t>
+  </si>
+  <si>
+    <t>Calon Pelaksana</t>
+  </si>
+  <si>
+    <t>Calon Teknisi</t>
+  </si>
+  <si>
+    <t>Calon Pelaksana Workshop</t>
+  </si>
+  <si>
+    <t>Calon Petugas Negative Check</t>
+  </si>
+  <si>
+    <t>Executive Vice President</t>
+  </si>
+  <si>
+    <t>Kepala UPT BYST</t>
+  </si>
+  <si>
+    <t>Pelaksana Workshop</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Power System 1</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Power System 2</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Signalling And Communication 1</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Signalling And Communication 2</t>
+  </si>
+  <si>
+    <t>Subunit of Workshop And OCC Signalling and Communication</t>
+  </si>
+  <si>
+    <t>Subunit of Workshop Power System And OCC Power</t>
+  </si>
+  <si>
+    <t>Vice President</t>
+  </si>
+  <si>
+    <t>Pelaksana Informasi dan Evaluasi</t>
+  </si>
+  <si>
+    <t>8 SB</t>
+  </si>
+  <si>
+    <t>HALIM MARZUQI</t>
+  </si>
+  <si>
+    <t>Manager STL Daop 8 Sb</t>
+  </si>
+  <si>
+    <t>PMP.251280.126008</t>
+  </si>
+  <si>
+    <t>HADI SUSANTO</t>
+  </si>
+  <si>
+    <t>QC STL 8A Bbt</t>
+  </si>
+  <si>
+    <t>PMP.290576.01040</t>
+  </si>
+  <si>
+    <t>EKO NURHADI</t>
+  </si>
+  <si>
+    <t>QC STL 8B Sgu</t>
+  </si>
+  <si>
+    <t>PMP.201277.126981</t>
+  </si>
+  <si>
+    <t>SRIYANTO</t>
+  </si>
+  <si>
+    <t>QC STL 8C Mr</t>
+  </si>
+  <si>
+    <t>PMP.220178.126561</t>
+  </si>
+  <si>
+    <t>NURHADI</t>
+  </si>
+  <si>
+    <t>QC STL 8D Ml</t>
+  </si>
+  <si>
+    <t>PMP.240271.01028</t>
+  </si>
+  <si>
+    <t>ROSIHAN ALI MUNANDAR</t>
+  </si>
+  <si>
+    <t>AM Informasi dan Evaluasi Daop 8 Sb</t>
+  </si>
+  <si>
+    <t>NUR ROSYALINDA HIDAYATI</t>
+  </si>
+  <si>
+    <t>AM Perencanaan dan Pengendalian Daop 8 Sb</t>
+  </si>
+  <si>
+    <t>PMP.211187.126351</t>
+  </si>
+  <si>
+    <t>EKO BUDY PRASETIJO</t>
+  </si>
+  <si>
+    <t>AM Spesifikasi dan Standarisasi Daop 8 Sb</t>
+  </si>
+  <si>
+    <t>PMP.070571.126241</t>
+  </si>
+  <si>
+    <t>FEBRIANTO RIZKI BUDIONO</t>
+  </si>
+  <si>
+    <t>PRP.18021992.37180</t>
+  </si>
+  <si>
+    <t>SUDARWATI</t>
+  </si>
+  <si>
+    <t>Pelaksana Perencanaan dan Pengendalian</t>
+  </si>
+  <si>
+    <t>EKAE WINARSIH</t>
+  </si>
+  <si>
+    <t>PRP.090679.38912</t>
+  </si>
+  <si>
+    <t>RIFKA MEI DIAH LESTARI</t>
+  </si>
+  <si>
+    <t>Pelaksana Spesifikasi dan Standarisasi</t>
+  </si>
+  <si>
+    <t>PRP.16081976.37890</t>
+  </si>
+  <si>
+    <t>EKO BUDI PRASETYO</t>
+  </si>
+  <si>
+    <t>Kepala UPT Workshop STL Sgu</t>
+  </si>
+  <si>
+    <t>WS Sb</t>
+  </si>
+  <si>
+    <t>PRP.120373.126187</t>
+  </si>
+  <si>
+    <t>ABDU YEPI MAHROBI</t>
+  </si>
+  <si>
     <t>Supervisor Perbaikan UPT Workshop Sintelis</t>
   </si>
   <si>
+    <t>PRP.02081986.30419</t>
+  </si>
+  <si>
+    <t>ANGGA FREDIYANTO</t>
+  </si>
+  <si>
     <t>Supervisor Rekayasa Perawatan UPT Workshop Sintelis</t>
   </si>
   <si>
-    <t>8 SB</t>
-  </si>
-  <si>
-    <t>HALIM MARZUQI</t>
-  </si>
-  <si>
-    <t>Manager STL Daop 8 Sb</t>
-  </si>
-  <si>
-    <t>HADI SUSANTO</t>
-  </si>
-  <si>
-    <t>QC STL 8A Bbt</t>
-  </si>
-  <si>
-    <t>EKO NURHADI</t>
-  </si>
-  <si>
-    <t>QC STL 8B Sgu</t>
-  </si>
-  <si>
-    <t>SRIYANTO</t>
-  </si>
-  <si>
-    <t>QC STL 8C Mr</t>
-  </si>
-  <si>
-    <t>NURHADI</t>
-  </si>
-  <si>
-    <t>QC STL 8D Ml</t>
-  </si>
-  <si>
-    <t>ROSIHAN ALI MUNANDAR</t>
-  </si>
-  <si>
-    <t>AM Informasi dan Evaluasi Daop 8 Sb</t>
-  </si>
-  <si>
-    <t>NUR ROSYALINDA HIDAYATI</t>
-  </si>
-  <si>
-    <t>AM Perencanaan dan Pengendalian Daop 8 Sb</t>
-  </si>
-  <si>
-    <t>EKO BUDY PRASETIJO</t>
-  </si>
-  <si>
-    <t>AM Spesifikasi dan Standarisasi Daop 8 Sb</t>
-  </si>
-  <si>
-    <t>FEBRIANTO RIZKI BUDIONO</t>
-  </si>
-  <si>
-    <t>Pelaksana Informasi dan Evaluasi</t>
-  </si>
-  <si>
-    <t>SUDARWATI</t>
-  </si>
-  <si>
-    <t>Pelaksana Perencanaan dan Pengendalian</t>
-  </si>
-  <si>
-    <t>EKAE WINARSIH</t>
-  </si>
-  <si>
-    <t>RIFKA MEI DIAH LESTARI</t>
-  </si>
-  <si>
-    <t>Pelaksana Spesifikasi dan Standarisasi</t>
-  </si>
-  <si>
-    <t>EKO BUDI PRASETYO</t>
-  </si>
-  <si>
-    <t>Kepala UPT Workshop STL Sgu</t>
-  </si>
-  <si>
-    <t>WS Sb</t>
-  </si>
-  <si>
-    <t>ABDU YEPI MAHROBI</t>
-  </si>
-  <si>
-    <t>ANGGA FREDIYANTO</t>
+    <t>PRP.18021990.32848</t>
   </si>
   <si>
     <t>ASEP SUPRIONO</t>
@@ -265,36 +421,57 @@
     <t>8.1 Bj</t>
   </si>
   <si>
+    <t>PRP.070277.128502</t>
+  </si>
+  <si>
     <t>AGUNG INDRA WAHYUDI</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 8.1 Bj</t>
   </si>
   <si>
+    <t>PRP.180886.00070</t>
+  </si>
+  <si>
     <t>JOHAND VAHRUDIN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 8.1 Bj</t>
   </si>
   <si>
+    <t>PRP.050688.00607</t>
+  </si>
+  <si>
     <t>PUTRA YUDHA ADITYA</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 8.1 Bj</t>
   </si>
   <si>
+    <t>PRP.15121992.38165</t>
+  </si>
+  <si>
     <t>YUDA DWI PRASTIA</t>
   </si>
   <si>
+    <t>PRP.25011995.37177</t>
+  </si>
+  <si>
     <t>FANI SULISTIAWAN</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 8.1 Bj</t>
   </si>
   <si>
+    <t>PRP.04081995.38161</t>
+  </si>
+  <si>
     <t>TIO HARPANI</t>
   </si>
   <si>
+    <t>PRP.120201.75615</t>
+  </si>
+  <si>
     <t>FAISAL ANWAR</t>
   </si>
   <si>
@@ -304,42 +481,72 @@
     <t>8.2 Bbt</t>
   </si>
   <si>
+    <t>PRP.210785.123428</t>
+  </si>
+  <si>
+    <t>PMP.210785.67150</t>
+  </si>
+  <si>
     <t>MOCHAMMAD SYARIF HIDAYATULLAH</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 8.2 Bbt</t>
   </si>
   <si>
+    <t>PRP.171288.00596</t>
+  </si>
+  <si>
     <t>IMAM SUGIRI</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 8.2 Bbt</t>
   </si>
   <si>
+    <t>PRP.190693.126259</t>
+  </si>
+  <si>
     <t>DIRGA RIANSYAH</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 8.2 Bbt</t>
   </si>
   <si>
+    <t>PRP.020398.122822</t>
+  </si>
+  <si>
     <t>ALWI KAHFI</t>
   </si>
   <si>
+    <t>PRP.291100.73718</t>
+  </si>
+  <si>
     <t>HANA YOZYA MIFTA' UL' ULUM</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 8.2 Bbt</t>
   </si>
   <si>
+    <t>PRP.290898.53996</t>
+  </si>
+  <si>
     <t>MUHAMMAD ADRIANSYAH</t>
   </si>
   <si>
+    <t>PRP.250505.73720</t>
+  </si>
+  <si>
     <t>AFIS SUNANI KHOIROISWA</t>
   </si>
   <si>
+    <t>PRP.20021992.38373</t>
+  </si>
+  <si>
     <t>RIZKI RAHADI</t>
   </si>
   <si>
+    <t>PRP.180689.00606</t>
+  </si>
+  <si>
     <t>MUKHAMMAD NUR HIDAYAT</t>
   </si>
   <si>
@@ -349,39 +556,63 @@
     <t>8.3 Lmg</t>
   </si>
   <si>
+    <t>PRP.260886.126710</t>
+  </si>
+  <si>
     <t>ABDUL ROKMAN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 8.3 Lmg</t>
   </si>
   <si>
+    <t>PRP.030390.128454</t>
+  </si>
+  <si>
     <t>FAHMI ACHMAD WIDIANTO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 8.3 Lmg</t>
   </si>
   <si>
+    <t>PRP.270587.123451</t>
+  </si>
+  <si>
     <t>ELMI FAKHRUDIN</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 8.3 Lmg</t>
   </si>
   <si>
+    <t>PRP.250988.00594</t>
+  </si>
+  <si>
     <t>YULIO ADHI SETYAWAN</t>
   </si>
   <si>
+    <t>PRP.10071994.37247</t>
+  </si>
+  <si>
     <t>IAN FENDA CANDRA KURNIAWAN</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 8.3 Lmg</t>
   </si>
   <si>
+    <t>PRP.281087.00577</t>
+  </si>
+  <si>
     <t>MOH. FAIZ ADILISTIO</t>
   </si>
   <si>
+    <t>PRP.17051993.37248</t>
+  </si>
+  <si>
     <t>HIKMAL RABBIN AZIZ</t>
   </si>
   <si>
+    <t>PRP.030403.75614</t>
+  </si>
+  <si>
     <t>EKO PRASTYO</t>
   </si>
   <si>
@@ -391,42 +622,72 @@
     <t>8.4 Kda</t>
   </si>
   <si>
+    <t>PRP.281176.128737</t>
+  </si>
+  <si>
+    <t>PMP.281176.67650</t>
+  </si>
+  <si>
     <t>WITJAKSONO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 8.4 Kda</t>
   </si>
   <si>
+    <t>PRP.240484.00319</t>
+  </si>
+  <si>
     <t>GUSNAWAN SAPUTRO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 8.4 Kda</t>
   </si>
   <si>
+    <t>PRP.200890.126015</t>
+  </si>
+  <si>
     <t>FITRA PRASWIYANTOYO</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 8.4 Kda</t>
   </si>
   <si>
+    <t>PRP.13051988.38164</t>
+  </si>
+  <si>
     <t>HALIMI BADRUIKHSANI</t>
   </si>
   <si>
+    <t>PRP.060402.56072</t>
+  </si>
+  <si>
     <t>MUHAMMAD ELANG PAMUNGKAS</t>
   </si>
   <si>
+    <t>PRP.260802.74228</t>
+  </si>
+  <si>
     <t>MOHAMMAD SYAFI'UDDIN</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 8.4 Kda</t>
   </si>
   <si>
+    <t>PRP.15111994.38177</t>
+  </si>
+  <si>
     <t>MOH. RISKIYANTO</t>
   </si>
   <si>
+    <t>PRP.25111995.38174</t>
+  </si>
+  <si>
     <t>ARDIANSYAH</t>
   </si>
   <si>
+    <t>PRP.130102.72843</t>
+  </si>
+  <si>
     <t>SUWARNO</t>
   </si>
   <si>
@@ -436,36 +697,60 @@
     <t>8.5 Sbi</t>
   </si>
   <si>
+    <t>PRP.220575.123446</t>
+  </si>
+  <si>
+    <t>PMP.220575.72303</t>
+  </si>
+  <si>
     <t>MOH. ABD MUFID</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas B 8.5 Sbi</t>
   </si>
   <si>
+    <t>PRP.131189.126016</t>
+  </si>
+  <si>
     <t>SOFYAN HIDAYAT</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas B 8.5 Sbi</t>
   </si>
   <si>
+    <t>PRP.190991.00661</t>
+  </si>
+  <si>
     <t>MUKHAMMAD MUSLIKH WIYATNO</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 8.5 Sbi</t>
   </si>
   <si>
+    <t>PRP.261088.00573</t>
+  </si>
+  <si>
     <t>MOCH. RIZAL</t>
   </si>
   <si>
+    <t>PRP.29031994.38159</t>
+  </si>
+  <si>
     <t>INDRA YULIANTO</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 8.5 Sbi</t>
   </si>
   <si>
+    <t>PRP.26071994.38156</t>
+  </si>
+  <si>
     <t>JOKO SAMPURNO</t>
   </si>
   <si>
+    <t>PRP.28081989.37941</t>
+  </si>
+  <si>
     <t>PETRUS KOEN TRIHARTANTO</t>
   </si>
   <si>
@@ -475,48 +760,81 @@
     <t>8.6 Sgu</t>
   </si>
   <si>
+    <t>PRP.260278.126631</t>
+  </si>
+  <si>
     <t>MOH. YUSUF ALFIAN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas B 8.6 Sgu</t>
   </si>
   <si>
+    <t>PRP.310587.125906</t>
+  </si>
+  <si>
     <t>MAULANA SOFIYAN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas B 8.6 Sgu</t>
   </si>
   <si>
+    <t>PRP.141287.127089</t>
+  </si>
+  <si>
     <t>AHMAD HARIS DWI FERDIANSYAH</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 8.6 Sgu</t>
   </si>
   <si>
+    <t>PRP.270702.50443</t>
+  </si>
+  <si>
     <t>IRWANSYAH SYAIFUDIN</t>
   </si>
   <si>
+    <t>PRP.050593.00626</t>
+  </si>
+  <si>
     <t>ARIFIN AS'AD MALIK AL SABAH</t>
   </si>
   <si>
+    <t>PRP.140391.40354</t>
+  </si>
+  <si>
     <t>RUDI PRASETYO</t>
   </si>
   <si>
+    <t>PRP.130793.00657</t>
+  </si>
+  <si>
     <t>MUHAMMAD FAHMI PRATAMA</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 8.6 Sgu</t>
   </si>
   <si>
+    <t>PRP.09061996.37821</t>
+  </si>
+  <si>
     <t>CELMI MARIO SANDY JAYA</t>
   </si>
   <si>
+    <t>PRP.160793.00627</t>
+  </si>
+  <si>
     <t>IRFAN RANGGA PRATAMA</t>
   </si>
   <si>
+    <t>PRP.150702.72295</t>
+  </si>
+  <si>
     <t>RIZQI NUR MAULANA</t>
   </si>
   <si>
+    <t>PRP.070400.56108</t>
+  </si>
+  <si>
     <t>ERIK SETIAWAN</t>
   </si>
   <si>
@@ -526,39 +844,66 @@
     <t>8.7 Wo</t>
   </si>
   <si>
+    <t>PRP.110787.126242</t>
+  </si>
+  <si>
+    <t>PMP.110787.67107</t>
+  </si>
+  <si>
     <t>MUHAMMAD CHOIRON</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 8.7 Wo</t>
   </si>
   <si>
+    <t>PRP.23051987.29648</t>
+  </si>
+  <si>
     <t>MUHAMMAD MACHBUB JUNAEDI</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 8.7 Wo</t>
   </si>
   <si>
+    <t>PRP.031186.125965</t>
+  </si>
+  <si>
     <t>MOCH. WISNU DWI WICAKSONO</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 8.7 Wo</t>
   </si>
   <si>
+    <t>PRP.02101991.37244</t>
+  </si>
+  <si>
     <t>DANAR WIRARAJA</t>
   </si>
   <si>
+    <t>PRP.24101988.38157</t>
+  </si>
+  <si>
     <t>MARIO GINOLA</t>
   </si>
   <si>
+    <t>PRP.080100.67655</t>
+  </si>
+  <si>
     <t>ADITYA SYAHRUDIN ABDILLAH</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 8.7 Wo</t>
   </si>
   <si>
+    <t>PRP.14091990.37182</t>
+  </si>
+  <si>
     <t>ARASI FATHUR ROZAK</t>
   </si>
   <si>
+    <t>PRP.19121997.37246</t>
+  </si>
+  <si>
     <t>ADITYO SURYO NUGROHO</t>
   </si>
   <si>
@@ -568,39 +913,66 @@
     <t>8.8 Mr</t>
   </si>
   <si>
+    <t>PRP.21081990.29516</t>
+  </si>
+  <si>
+    <t>PMP.210890.70714</t>
+  </si>
+  <si>
     <t>TIGOR ARI SASONGKO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 8.8 Mr</t>
   </si>
   <si>
+    <t>PRP.080586.123450</t>
+  </si>
+  <si>
     <t>SELLY YULANDA</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 8.8 Mr</t>
   </si>
   <si>
+    <t>PRP.12071993.37245</t>
+  </si>
+  <si>
     <t>YOUANDA SETYA RAHARJO</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 8.8 Mr</t>
   </si>
   <si>
+    <t>PRP.23031995.36994</t>
+  </si>
+  <si>
     <t>WAHYU ARIYANTO</t>
   </si>
   <si>
+    <t>PRP.03041993.36996</t>
+  </si>
+  <si>
     <t>MOCH. TAUFIK</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 8.8 Mr</t>
   </si>
   <si>
+    <t>PRP.09121987.36993</t>
+  </si>
+  <si>
     <t>ACHMAD BAYU PRATAMA</t>
   </si>
   <si>
+    <t>PRP.19071994.36995</t>
+  </si>
+  <si>
     <t>MUHAMMAD KAUTSAR FATCHURROHMAN</t>
   </si>
   <si>
+    <t>PRP.011100.56875</t>
+  </si>
+  <si>
     <t>HERMAN</t>
   </si>
   <si>
@@ -610,39 +982,66 @@
     <t>8.9 Sda</t>
   </si>
   <si>
+    <t>PRP.030286.126011</t>
+  </si>
+  <si>
+    <t>PMP.030286.71209</t>
+  </si>
+  <si>
     <t>JONI IRAWAN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas B 8.9 Sda</t>
   </si>
   <si>
+    <t>PRP.011189.126269</t>
+  </si>
+  <si>
     <t>SUPARMAN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas B 8.9 Sda</t>
   </si>
   <si>
+    <t>PRP.261090.64372</t>
+  </si>
+  <si>
     <t>MOKHAMAD FUDLOILY</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 8.9 Sda</t>
   </si>
   <si>
+    <t>PRP.281284.00566</t>
+  </si>
+  <si>
     <t>BAGASKORO ADI SUWARNO BUDIANTO</t>
   </si>
   <si>
+    <t>PRP.070102.68026</t>
+  </si>
+  <si>
     <t>MOCHAMAD ALFIAN PUTRA PURNAMA</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 8.9 Sda</t>
   </si>
   <si>
+    <t>PRP.141192.00654</t>
+  </si>
+  <si>
     <t>DIAN PURNOMO</t>
   </si>
   <si>
+    <t>PRP.040893.39100</t>
+  </si>
+  <si>
     <t>ADAM ENGGAR BUDIANTORO</t>
   </si>
   <si>
+    <t>PRP.02061994.38062</t>
+  </si>
+  <si>
     <t>SOERJONO</t>
   </si>
   <si>
@@ -652,27 +1051,42 @@
     <t>8.10 Bg</t>
   </si>
   <si>
+    <t>PMP.161071.67729</t>
+  </si>
+  <si>
     <t>MOCHAMAD CHASAN BASORI</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 8.10 Bg</t>
   </si>
   <si>
+    <t>PRP.051189.128453</t>
+  </si>
+  <si>
     <t>MOKH. SAIFUDIN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 8.10 Bg</t>
   </si>
   <si>
+    <t>PRP.271189.126262</t>
+  </si>
+  <si>
     <t>RAMDHANY BAGUS WINATA</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 8.10 Bg</t>
   </si>
   <si>
+    <t>PRP.161102.60564</t>
+  </si>
+  <si>
     <t>DWI CAHYO ARIFANDI</t>
   </si>
   <si>
+    <t>PRP.160786.00569</t>
+  </si>
+  <si>
     <t>MUHAMMAD FIRZA APRIATAMA</t>
   </si>
   <si>
@@ -682,12 +1096,21 @@
     <t>PNC Preventif UPT Resor STL 8.10 Bg</t>
   </si>
   <si>
+    <t>PRP.081186.00625</t>
+  </si>
+  <si>
     <t>IKHVANDRI ZALVI</t>
   </si>
   <si>
+    <t>PRP.270303.67656</t>
+  </si>
+  <si>
     <t>A'AN FARISKA RAMANDA PUTRA</t>
   </si>
   <si>
+    <t>PRP.080195.38906</t>
+  </si>
+  <si>
     <t>IWAN ARIF WICAKSONO</t>
   </si>
   <si>
@@ -697,42 +1120,69 @@
     <t>8.11 Ml</t>
   </si>
   <si>
+    <t>PMP.010988.65584</t>
+  </si>
+  <si>
     <t>MUHAMMAD CHOIRUL ANAM</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 8.11 Ml</t>
   </si>
   <si>
+    <t>PRP.050588.00248</t>
+  </si>
+  <si>
     <t>JUNIFAN FATKHURROCHMAN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 8.11 Ml</t>
   </si>
   <si>
+    <t>PRP.140687.126010</t>
+  </si>
+  <si>
     <t>ANDANI LUTFY INSYANI</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 8.11 Ml</t>
   </si>
   <si>
+    <t>PRP.180595.40345</t>
+  </si>
+  <si>
     <t>ACHMAD SOLECHUDIN</t>
   </si>
   <si>
+    <t>PRP.27071993.38166</t>
+  </si>
+  <si>
     <t>ISHAQ ZUFI FIRDAUSY</t>
   </si>
   <si>
+    <t>PRP.080702.67836</t>
+  </si>
+  <si>
     <t>FREDI DUWI KUSUMA</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 8.11 Ml</t>
   </si>
   <si>
+    <t>PRP.10101991.38163</t>
+  </si>
+  <si>
     <t>MOCHAMMAD LUTFI SETIAWAN</t>
   </si>
   <si>
+    <t>PRP.230793.00624</t>
+  </si>
+  <si>
     <t>MUHAMMAD BAHA'UDDIN</t>
   </si>
   <si>
+    <t>PRP.210992.00575</t>
+  </si>
+  <si>
     <t>ARI FERIANTO</t>
   </si>
   <si>
@@ -742,325 +1192,64 @@
     <t>8.12 Kpn</t>
   </si>
   <si>
+    <t>PRP.261088.125967</t>
+  </si>
+  <si>
+    <t>PMP.261088.64919</t>
+  </si>
+  <si>
     <t>YANU ADI SAPUTRO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 8.12 Kpn</t>
   </si>
   <si>
+    <t>PRP.251089.125685</t>
+  </si>
+  <si>
     <t>SYAMSUL HIDAYAT</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 8.12 Kpn</t>
   </si>
   <si>
+    <t>PRP.020388.126260</t>
+  </si>
+  <si>
     <t>IWAN SETIYO BUDI</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 8.12 Kpn</t>
   </si>
   <si>
+    <t>PRP.11061994.37795</t>
+  </si>
+  <si>
     <t>RIAN CAHYA NUGRAHA</t>
   </si>
   <si>
+    <t>PRP.06011992.38061</t>
+  </si>
+  <si>
     <t>KOKO WIDIYASTANTO</t>
   </si>
   <si>
+    <t>PRP.20101989.38162</t>
+  </si>
+  <si>
     <t>RYAN PERMADI</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 8.12 Kpn</t>
   </si>
   <si>
+    <t>PRP.280292.39450</t>
+  </si>
+  <si>
     <t>DEDY FERDIAN</t>
   </si>
   <si>
-    <t>PMP.251280.126008</t>
-  </si>
-  <si>
-    <t>PMP. 290576. 01040</t>
-  </si>
-  <si>
-    <t>PMP.201277.126981</t>
-  </si>
-  <si>
-    <t>PMP.220178.126561</t>
-  </si>
-  <si>
-    <t>PMP.240271.01028</t>
-  </si>
-  <si>
-    <t>PMP. 310872. 126736</t>
-  </si>
-  <si>
-    <t>PMP.211187.126351</t>
-  </si>
-  <si>
-    <t>PMP.070571.126241</t>
-  </si>
-  <si>
-    <t>PRP.18021992.37180</t>
-  </si>
-  <si>
-    <t>PRP.090679.38912</t>
-  </si>
-  <si>
-    <t>PRP.16081976.37890</t>
-  </si>
-  <si>
-    <t>PRP.02081986.30419</t>
-  </si>
-  <si>
-    <t>PRP.18021990.32848</t>
-  </si>
-  <si>
-    <t>PRP.180886.00070</t>
-  </si>
-  <si>
-    <t>PRP.050688.00607</t>
-  </si>
-  <si>
-    <t>PRP.15121992.38165</t>
-  </si>
-  <si>
-    <t>PRP.120201.75615</t>
-  </si>
-  <si>
-    <t>PRP.210785.123428</t>
-  </si>
-  <si>
-    <t>PRP.190693.126259</t>
-  </si>
-  <si>
-    <t>PRP.020398.122822</t>
-  </si>
-  <si>
-    <t>PRP.291100.73718</t>
-  </si>
-  <si>
-    <t>PRP.290898.53996</t>
-  </si>
-  <si>
-    <t>PRP.250505.73720</t>
-  </si>
-  <si>
-    <t>PRP.20021992.38373</t>
-  </si>
-  <si>
-    <t>PRP.180689.00606</t>
-  </si>
-  <si>
-    <t>PRP.260886.126710</t>
-  </si>
-  <si>
-    <t>PRP.270587.123451</t>
-  </si>
-  <si>
-    <t>PRP.250988.00594</t>
-  </si>
-  <si>
-    <t>PRP.10071994.37247</t>
-  </si>
-  <si>
-    <t>PRP.281087.00577</t>
-  </si>
-  <si>
-    <t>PRP.17051993.37248</t>
-  </si>
-  <si>
-    <t>PRP.030403.75614</t>
-  </si>
-  <si>
-    <t>PRP.281176.128737</t>
-  </si>
-  <si>
-    <t>PRP.240484.00319</t>
-  </si>
-  <si>
-    <t>PRP.200890.126015</t>
-  </si>
-  <si>
-    <t>PRP.13051988.38164</t>
-  </si>
-  <si>
-    <t>PRP.260802.74228</t>
-  </si>
-  <si>
-    <t>PRP.25111995.38174</t>
-  </si>
-  <si>
-    <t>PRP.130102.72843</t>
-  </si>
-  <si>
-    <t>PRP.220575.123446</t>
-  </si>
-  <si>
-    <t>PRP.131189.126016</t>
-  </si>
-  <si>
-    <t>PRP.190991.00661</t>
-  </si>
-  <si>
-    <t>PRP.261088.00573</t>
-  </si>
-  <si>
-    <t>PRP.26071994.38156</t>
-  </si>
-  <si>
-    <t>PRP.28081989.37941</t>
-  </si>
-  <si>
-    <t>PRP.270702.50443</t>
-  </si>
-  <si>
-    <t>PRP.140391.40354</t>
-  </si>
-  <si>
-    <t>PRP.130793.00657</t>
-  </si>
-  <si>
-    <t>PRP.160793.00627</t>
-  </si>
-  <si>
-    <t>PRP.150702.72295</t>
-  </si>
-  <si>
-    <t>PRP.031186.125965</t>
-  </si>
-  <si>
-    <t>PRP.02101991.37244</t>
-  </si>
-  <si>
-    <t>PRP.24101988.38157</t>
-  </si>
-  <si>
-    <t>PRP.080100.67655</t>
-  </si>
-  <si>
-    <t>PRP.14091990.37182</t>
-  </si>
-  <si>
-    <t>PRP.19121997.37246</t>
-  </si>
-  <si>
-    <t>PRP.080586.123450</t>
-  </si>
-  <si>
-    <t>PRP.12071993.37245</t>
-  </si>
-  <si>
-    <t>PRP.03041993.36996</t>
-  </si>
-  <si>
-    <t>PRP.09121987.36993</t>
-  </si>
-  <si>
-    <t>PRP.19071994.36995</t>
-  </si>
-  <si>
-    <t>PRP.011100.56875</t>
-  </si>
-  <si>
-    <t>PRP.030286.126011</t>
-  </si>
-  <si>
-    <t>PRP.261090.64372</t>
-  </si>
-  <si>
-    <t>PRP.281284.00566</t>
-  </si>
-  <si>
-    <t>PRP.070102.68026</t>
-  </si>
-  <si>
-    <t>PRP.141192.00654</t>
-  </si>
-  <si>
-    <t>PRP.040893.39100</t>
-  </si>
-  <si>
-    <t>PRP.161071.128736</t>
-  </si>
-  <si>
-    <t>PRP.271189.126262</t>
-  </si>
-  <si>
-    <t>PRP.161102.60564</t>
-  </si>
-  <si>
-    <t>PRP.160786.00569</t>
-  </si>
-  <si>
-    <t>PRP.081186.00625</t>
-  </si>
-  <si>
-    <t>PRP.270303.67656</t>
-  </si>
-  <si>
-    <t>PRP.080195.38906</t>
-  </si>
-  <si>
-    <t>PMP.010988.65584</t>
-  </si>
-  <si>
-    <t>PRP.050588.00248</t>
-  </si>
-  <si>
-    <t>PRP.140687.126010</t>
-  </si>
-  <si>
-    <t>PRP.180595.40345</t>
-  </si>
-  <si>
-    <t>PRP.27071993.38166</t>
-  </si>
-  <si>
-    <t>PRP.080702.67836</t>
-  </si>
-  <si>
-    <t>PRP.10101991.38163</t>
-  </si>
-  <si>
-    <t>PRP.210992.00575</t>
-  </si>
-  <si>
-    <t>PRP.261088.125967</t>
-  </si>
-  <si>
-    <t>PRP.020388.126260</t>
-  </si>
-  <si>
-    <t>PRP.11061994.37795</t>
-  </si>
-  <si>
-    <t>PRP.06011992.38061</t>
-  </si>
-  <si>
-    <t>PRP.20101989.38162</t>
-  </si>
-  <si>
     <t>PRP.080989.00603</t>
-  </si>
-  <si>
-    <t>PMP.290576.01040</t>
-  </si>
-  <si>
-    <t>PMP.210785.67150</t>
-  </si>
-  <si>
-    <t>PMP.281176.67650</t>
-  </si>
-  <si>
-    <t>PMP.220575.72303</t>
-  </si>
-  <si>
-    <t>PMP.030286.71209</t>
-  </si>
-  <si>
-    <t>PMP.161071.67729</t>
-  </si>
-  <si>
-    <t>PMP.261088.64919</t>
   </si>
 </sst>
 </file>
@@ -1131,9 +1320,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1142,8 +1328,11 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1447,30 +1636,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T117"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:T200"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" zeroHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.86328125" style="2" customWidth="1"/>
     <col min="2" max="2" width="27.265625" style="3" customWidth="1"/>
     <col min="3" max="3" width="7.86328125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.59765625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.59765625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="32" style="4" customWidth="1"/>
-    <col min="7" max="7" width="8.46484375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.1328125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.53125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="32" style="7" customWidth="1"/>
+    <col min="7" max="7" width="12.1328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.1328125" style="5" customWidth="1"/>
     <col min="9" max="9" width="7.06640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="10.73046875" style="2" customWidth="1"/>
-    <col min="11" max="13" width="13.1328125" style="6" customWidth="1"/>
+    <col min="11" max="13" width="13.1328125" style="5" customWidth="1"/>
     <col min="14" max="14" width="22" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13.1328125" style="6" customWidth="1"/>
+    <col min="15" max="15" width="13.1328125" style="5" customWidth="1"/>
     <col min="16" max="17" width="22" style="2" customWidth="1"/>
-    <col min="18" max="18" width="13.1328125" style="6" customWidth="1"/>
-    <col min="19" max="19" width="22" style="2" customWidth="1"/>
-    <col min="20" max="20" width="22" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.1328125" style="5" customWidth="1"/>
+    <col min="19" max="20" width="22" style="2" customWidth="1"/>
     <col min="21" max="16384" width="9.06640625" style="3" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="5" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:20" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1492,7 +1680,7 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -1501,19 +1689,19 @@
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>13</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -1522,7 +1710,7 @@
       <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="S1" s="1" t="s">
@@ -1534,10 +1722,10 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2">
         <v>50553</v>
@@ -1548,13 +1736,13 @@
       <c r="E2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>48</v>
+      <c r="F2" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>45787</v>
       </c>
       <c r="I2" s="2">
@@ -1563,34 +1751,31 @@
       <c r="J2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="5">
         <v>39845</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="5">
         <v>29580</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="5">
         <v>50041</v>
       </c>
-      <c r="N2" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="O2" s="6">
+      <c r="Q2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="R2" s="5">
         <v>47114</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="R2" s="6">
-        <v>47114</v>
+      <c r="S2" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2">
         <v>44177</v>
@@ -1601,13 +1786,13 @@
       <c r="E3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>50</v>
+      <c r="F3" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>45627</v>
       </c>
       <c r="I3" s="2">
@@ -1616,36 +1801,28 @@
       <c r="J3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <v>35217</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>27909</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="5">
         <v>48366</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="O3" s="6">
-        <v>45766</v>
-      </c>
-      <c r="P3" s="3"/>
       <c r="Q3" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="R3" s="6">
+        <v>87</v>
+      </c>
+      <c r="R3" s="5">
         <v>47324</v>
       </c>
-      <c r="S3" s="3"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2">
         <v>45789</v>
@@ -1656,13 +1833,13 @@
       <c r="E4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>52</v>
+      <c r="F4" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>45884</v>
       </c>
       <c r="I4" s="2">
@@ -1671,36 +1848,31 @@
       <c r="J4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>35490</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="5">
         <v>28479</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="5">
         <v>48945</v>
       </c>
-      <c r="N4" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="O4" s="6">
+      <c r="Q4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="R4" s="5">
         <v>46916</v>
       </c>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="R4" s="6">
-        <v>46916</v>
-      </c>
-      <c r="S4" s="3"/>
+      <c r="S4" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="C5" s="2">
         <v>43411</v>
@@ -1711,13 +1883,13 @@
       <c r="E5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>54</v>
+      <c r="F5" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>45945</v>
       </c>
       <c r="I5" s="2">
@@ -1726,35 +1898,31 @@
       <c r="J5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <v>35217</v>
       </c>
-      <c r="L5" s="6">
-        <v>28512</v>
-      </c>
-      <c r="M5" s="6">
+      <c r="L5" s="5">
+        <v>25988</v>
+      </c>
+      <c r="M5" s="5">
         <v>48976</v>
       </c>
-      <c r="N5" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="O5" s="6">
+      <c r="Q5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="R5" s="5">
         <v>46837</v>
       </c>
-      <c r="Q5" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="R5" s="6">
-        <v>46837</v>
-      </c>
-      <c r="S5" s="3"/>
+      <c r="S5" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="C6" s="2">
         <v>42076</v>
@@ -1765,14 +1933,14 @@
       <c r="E6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>56</v>
+      <c r="F6" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="6">
-        <v>46060</v>
+      <c r="H6" s="5">
+        <v>45352</v>
       </c>
       <c r="I6" s="2">
         <v>11</v>
@@ -1780,35 +1948,31 @@
       <c r="J6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>34669</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <v>25988</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="5">
         <v>46447</v>
       </c>
-      <c r="N6" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="O6" s="6">
+      <c r="Q6" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="R6" s="5">
         <v>46965</v>
       </c>
-      <c r="Q6" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="R6" s="6">
-        <v>46965</v>
-      </c>
-      <c r="S6" s="3"/>
+      <c r="S6" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2">
         <v>41119</v>
@@ -1819,13 +1983,13 @@
       <c r="E7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>58</v>
+      <c r="F7" s="7" t="s">
+        <v>98</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>45641</v>
       </c>
       <c r="I7" s="2">
@@ -1834,34 +1998,22 @@
       <c r="J7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="6">
-        <v>33981</v>
-      </c>
-      <c r="L7" s="6">
+      <c r="K7" s="5">
+        <v>34304</v>
+      </c>
+      <c r="L7" s="5">
         <v>26542</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="5">
         <v>46997</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="O7" s="6">
-        <v>45696</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="R7" s="6">
-        <v>45696</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2">
         <v>62904</v>
@@ -1872,13 +2024,13 @@
       <c r="E8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>60</v>
+      <c r="F8" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>45641</v>
       </c>
       <c r="I8" s="2">
@@ -1887,35 +2039,31 @@
       <c r="J8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="5">
         <v>41456</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="5">
         <v>32102</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="5">
         <v>52566</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="O8" s="6">
+      <c r="Q8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="R8" s="5">
         <v>46951</v>
       </c>
-      <c r="Q8" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="R8" s="6">
-        <v>46951</v>
-      </c>
-      <c r="S8" s="3"/>
+      <c r="S8" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2">
         <v>42079</v>
@@ -1926,14 +2074,14 @@
       <c r="E9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>62</v>
+      <c r="F9" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="6">
-        <v>44927</v>
+      <c r="H9" s="5">
+        <v>44669</v>
       </c>
       <c r="I9" s="2">
         <v>10</v>
@@ -1941,35 +2089,31 @@
       <c r="J9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="6">
-        <v>34346</v>
-      </c>
-      <c r="L9" s="6">
+      <c r="K9" s="5">
+        <v>34669</v>
+      </c>
+      <c r="L9" s="5">
         <v>26060</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="5">
         <v>46539</v>
       </c>
-      <c r="N9" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="O9" s="6">
+      <c r="Q9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="R9" s="5">
         <v>46950</v>
       </c>
-      <c r="Q9" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="R9" s="6">
-        <v>46950</v>
-      </c>
-      <c r="S9" s="3"/>
+      <c r="S9" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="C10" s="2">
         <v>69127</v>
@@ -1980,13 +2124,13 @@
       <c r="E10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>64</v>
+      <c r="F10" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <v>45093</v>
       </c>
       <c r="I10" s="2">
@@ -1995,28 +2139,31 @@
       <c r="J10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L10" s="6">
+      <c r="K10" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L10" s="5">
         <v>33652</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="5">
         <v>54118</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="O10" s="6">
+        <v>106</v>
+      </c>
+      <c r="O10" s="5">
         <v>46259</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2">
         <v>56165</v>
@@ -2027,14 +2174,14 @@
       <c r="E11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>66</v>
+      <c r="F11" s="7" t="s">
+        <v>108</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="6">
-        <v>44927</v>
+      <c r="H11" s="5">
+        <v>44348</v>
       </c>
       <c r="I11" s="2">
         <v>4</v>
@@ -2042,23 +2189,22 @@
       <c r="J11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="6">
-        <v>40185</v>
-      </c>
-      <c r="L11" s="6">
+      <c r="K11" s="5">
+        <v>40360</v>
+      </c>
+      <c r="L11" s="5">
         <v>28082</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="5">
         <v>48549</v>
       </c>
-      <c r="S11" s="3"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="C12" s="2">
         <v>51497</v>
@@ -2069,14 +2215,14 @@
       <c r="E12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>66</v>
+      <c r="F12" s="7" t="s">
+        <v>108</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="6">
-        <v>44927</v>
+      <c r="H12" s="5">
+        <v>44348</v>
       </c>
       <c r="I12" s="2">
         <v>4</v>
@@ -2084,29 +2230,31 @@
       <c r="J12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K12" s="6">
-        <v>39453</v>
-      </c>
-      <c r="L12" s="6">
+      <c r="K12" s="5">
+        <v>39600</v>
+      </c>
+      <c r="L12" s="5">
         <v>29015</v>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="5">
         <v>49491</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="O12" s="6">
+        <v>110</v>
+      </c>
+      <c r="O12" s="5">
         <v>46407</v>
       </c>
-      <c r="S12" s="3"/>
+      <c r="P12" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="C13" s="2">
         <v>56168</v>
@@ -2117,14 +2265,14 @@
       <c r="E13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>69</v>
+      <c r="F13" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="6">
-        <v>44927</v>
+      <c r="H13" s="5">
+        <v>42467</v>
       </c>
       <c r="I13" s="2">
         <v>4</v>
@@ -2132,29 +2280,31 @@
       <c r="J13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K13" s="6">
-        <v>40185</v>
-      </c>
-      <c r="L13" s="6">
+      <c r="K13" s="5">
+        <v>40360</v>
+      </c>
+      <c r="L13" s="5">
         <v>27988</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="5">
         <v>48458</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="O13" s="6">
+        <v>113</v>
+      </c>
+      <c r="O13" s="5">
         <v>46263</v>
       </c>
-      <c r="S13" s="3"/>
+      <c r="P13" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="C14" s="2">
         <v>43388</v>
@@ -2165,13 +2315,13 @@
       <c r="E14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>71</v>
+      <c r="F14" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H14" s="6">
+        <v>116</v>
+      </c>
+      <c r="H14" s="5">
         <v>45371</v>
       </c>
       <c r="I14" s="2">
@@ -2180,23 +2330,31 @@
       <c r="J14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <v>35217</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="5">
         <v>26735</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="5">
         <v>47209</v>
       </c>
-      <c r="S14" s="3"/>
+      <c r="N14" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="O14" s="5">
+        <v>47295</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="15" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="C15" s="2">
         <v>55174</v>
@@ -2207,14 +2365,14 @@
       <c r="E15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>44</v>
+      <c r="F15" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H15" s="6">
-        <v>44927</v>
+        <v>116</v>
+      </c>
+      <c r="H15" s="5">
+        <v>44896</v>
       </c>
       <c r="I15" s="2">
         <v>8</v>
@@ -2222,29 +2380,31 @@
       <c r="J15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="5">
         <v>40163</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="5">
         <v>31626</v>
       </c>
-      <c r="M15" s="6">
+      <c r="M15" s="5">
         <v>52110</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="O15" s="6">
+        <v>120</v>
+      </c>
+      <c r="O15" s="5">
         <v>47370</v>
       </c>
-      <c r="S15" s="3"/>
+      <c r="P15" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="16" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="C16" s="2">
         <v>53887</v>
@@ -2255,13 +2415,13 @@
       <c r="E16" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>45</v>
+      <c r="F16" s="7" t="s">
+        <v>122</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H16" s="6">
+        <v>116</v>
+      </c>
+      <c r="H16" s="5">
         <v>45703</v>
       </c>
       <c r="I16" s="2">
@@ -2270,29 +2430,31 @@
       <c r="J16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="5">
         <v>39814</v>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="5">
         <v>32922</v>
       </c>
-      <c r="M16" s="6">
+      <c r="M16" s="5">
         <v>53387</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="O16" s="6">
+        <v>123</v>
+      </c>
+      <c r="O16" s="5">
         <v>47295</v>
       </c>
-      <c r="S16" s="3"/>
+      <c r="P16" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="C17" s="2">
         <v>48855</v>
@@ -2303,13 +2465,13 @@
       <c r="E17" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>76</v>
+      <c r="F17" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H17" s="6">
+        <v>126</v>
+      </c>
+      <c r="H17" s="5">
         <v>45809</v>
       </c>
       <c r="I17" s="2">
@@ -2318,23 +2480,31 @@
       <c r="J17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="5">
         <v>38899</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="5">
         <v>28163</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17" s="5">
         <v>48639</v>
       </c>
-      <c r="S17" s="3"/>
+      <c r="N17" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="O17" s="5">
+        <v>47370</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="18" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="C18" s="2">
         <v>55176</v>
@@ -2345,14 +2515,14 @@
       <c r="E18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>79</v>
+      <c r="F18" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18" s="6">
-        <v>46023</v>
+        <v>126</v>
+      </c>
+      <c r="H18" s="5">
+        <v>45017</v>
       </c>
       <c r="I18" s="2">
         <v>7</v>
@@ -2360,28 +2530,31 @@
       <c r="J18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="5">
         <v>40163</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="5">
         <v>31642</v>
       </c>
-      <c r="M18" s="6">
+      <c r="M18" s="5">
         <v>52110</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="O18" s="6">
+        <v>130</v>
+      </c>
+      <c r="O18" s="5">
         <v>46851</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="C19" s="2">
         <v>62125</v>
@@ -2392,13 +2565,13 @@
       <c r="E19" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>81</v>
+      <c r="F19" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H19" s="6">
+        <v>126</v>
+      </c>
+      <c r="H19" s="5">
         <v>45519</v>
       </c>
       <c r="I19" s="2">
@@ -2407,29 +2580,31 @@
       <c r="J19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="5">
         <v>41153</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="5">
         <v>32299</v>
       </c>
-      <c r="M19" s="6">
+      <c r="M19" s="5">
         <v>52779</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="O19" s="6">
+        <v>133</v>
+      </c>
+      <c r="O19" s="5">
         <v>47295</v>
       </c>
-      <c r="S19" s="3"/>
+      <c r="P19" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="C20" s="2">
         <v>69116</v>
@@ -2440,14 +2615,14 @@
       <c r="E20" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>83</v>
+      <c r="F20" s="7" t="s">
+        <v>135</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H20" s="6">
-        <v>46023</v>
+        <v>126</v>
+      </c>
+      <c r="H20" s="5">
+        <v>43164</v>
       </c>
       <c r="I20" s="2">
         <v>5</v>
@@ -2455,29 +2630,31 @@
       <c r="J20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K20" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L20" s="6">
+      <c r="K20" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L20" s="5">
         <v>33953</v>
       </c>
-      <c r="M20" s="6">
+      <c r="M20" s="5">
         <v>54424</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="O20" s="6">
+        <v>136</v>
+      </c>
+      <c r="O20" s="5">
         <v>46305</v>
       </c>
-      <c r="S20" s="3"/>
+      <c r="P20" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="C21" s="2">
         <v>70799</v>
@@ -2488,14 +2665,14 @@
       <c r="E21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>83</v>
+      <c r="F21" s="7" t="s">
+        <v>135</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H21" s="6">
-        <v>44927</v>
+        <v>126</v>
+      </c>
+      <c r="H21" s="5">
+        <v>43328</v>
       </c>
       <c r="I21" s="2">
         <v>5</v>
@@ -2503,23 +2680,31 @@
       <c r="J21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="5">
         <v>42725</v>
       </c>
-      <c r="L21" s="6">
-        <v>32839</v>
-      </c>
-      <c r="M21" s="6">
-        <v>53297</v>
-      </c>
-      <c r="S21" s="3"/>
+      <c r="L21" s="5">
+        <v>34724</v>
+      </c>
+      <c r="M21" s="5">
+        <v>55185</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="O21" s="5">
+        <v>46259</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="C22" s="2">
         <v>69992</v>
@@ -2530,14 +2715,14 @@
       <c r="E22" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>86</v>
+      <c r="F22" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H22" s="6">
-        <v>44927</v>
+        <v>126</v>
+      </c>
+      <c r="H22" s="5">
+        <v>44091</v>
       </c>
       <c r="I22" s="2">
         <v>5</v>
@@ -2545,23 +2730,31 @@
       <c r="J22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K22" s="6">
+      <c r="K22" s="5">
         <v>42597</v>
       </c>
-      <c r="L22" s="6">
+      <c r="L22" s="5">
         <v>34915</v>
       </c>
-      <c r="M22" s="6">
+      <c r="M22" s="5">
         <v>55397</v>
       </c>
-      <c r="S22" s="3"/>
+      <c r="N22" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="O22" s="5">
+        <v>46305</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="C23" s="2">
         <v>75404</v>
@@ -2572,13 +2765,13 @@
       <c r="E23" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>86</v>
+      <c r="F23" s="7" t="s">
+        <v>140</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H23" s="6">
+        <v>126</v>
+      </c>
+      <c r="H23" s="5">
         <v>45611</v>
       </c>
       <c r="I23" s="2">
@@ -2587,29 +2780,31 @@
       <c r="J23" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="5">
         <v>44958</v>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="5">
         <v>36934</v>
       </c>
-      <c r="M23" s="6">
+      <c r="M23" s="5">
         <v>57405</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="O23" s="6">
+        <v>143</v>
+      </c>
+      <c r="O23" s="5">
         <v>47370</v>
       </c>
-      <c r="S23" s="3"/>
+      <c r="P23" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="C24" s="2">
         <v>49750</v>
@@ -2620,14 +2815,14 @@
       <c r="E24" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>89</v>
+      <c r="F24" s="7" t="s">
+        <v>145</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H24" s="6">
-        <v>44927</v>
+        <v>146</v>
+      </c>
+      <c r="H24" s="5">
+        <v>44883</v>
       </c>
       <c r="I24" s="2">
         <v>8</v>
@@ -2635,35 +2830,40 @@
       <c r="J24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K24" s="6">
-        <v>39814</v>
-      </c>
-      <c r="L24" s="6">
+      <c r="K24" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L24" s="5">
         <v>31249</v>
       </c>
-      <c r="M24" s="6">
+      <c r="M24" s="5">
         <v>51714</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="O24" s="6">
+        <v>147</v>
+      </c>
+      <c r="O24" s="5">
         <v>47005</v>
       </c>
+      <c r="P24" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q24" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="R24" s="6">
+        <v>148</v>
+      </c>
+      <c r="R24" s="5">
         <v>47097</v>
       </c>
-      <c r="S24" s="3"/>
+      <c r="S24" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="25" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>91</v>
+        <v>149</v>
       </c>
       <c r="C25" s="2">
         <v>53746</v>
@@ -2674,14 +2874,14 @@
       <c r="E25" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>92</v>
+      <c r="F25" s="7" t="s">
+        <v>150</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H25" s="6">
-        <v>46023</v>
+        <v>146</v>
+      </c>
+      <c r="H25" s="5">
+        <v>45017</v>
       </c>
       <c r="I25" s="2">
         <v>7</v>
@@ -2689,22 +2889,31 @@
       <c r="J25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K25" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L25" s="6">
+      <c r="K25" s="5">
+        <v>39814</v>
+      </c>
+      <c r="L25" s="5">
         <v>32494</v>
       </c>
-      <c r="M25" s="6">
+      <c r="M25" s="5">
         <v>52963</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="O25" s="5">
+        <v>46610</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="C26" s="2">
         <v>61481</v>
@@ -2715,14 +2924,14 @@
       <c r="E26" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>94</v>
+      <c r="F26" s="7" t="s">
+        <v>153</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H26" s="6">
-        <v>44927</v>
+        <v>146</v>
+      </c>
+      <c r="H26" s="5">
+        <v>44883</v>
       </c>
       <c r="I26" s="2">
         <v>7</v>
@@ -2730,29 +2939,31 @@
       <c r="J26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K26" s="6">
-        <v>40552</v>
-      </c>
-      <c r="L26" s="6">
+      <c r="K26" s="5">
+        <v>40787</v>
+      </c>
+      <c r="L26" s="5">
         <v>34139</v>
       </c>
-      <c r="M26" s="6">
+      <c r="M26" s="5">
         <v>54605</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="O26" s="6">
+        <v>154</v>
+      </c>
+      <c r="O26" s="5">
         <v>47054</v>
       </c>
-      <c r="S26" s="3"/>
+      <c r="P26" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="C27" s="2">
         <v>71457</v>
@@ -2763,14 +2974,14 @@
       <c r="E27" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>96</v>
+      <c r="F27" s="7" t="s">
+        <v>156</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H27" s="6">
-        <v>44927</v>
+        <v>146</v>
+      </c>
+      <c r="H27" s="5">
+        <v>43375</v>
       </c>
       <c r="I27" s="2">
         <v>5</v>
@@ -2778,29 +2989,31 @@
       <c r="J27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K27" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L27" s="6">
+      <c r="K27" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L27" s="5">
         <v>35856</v>
       </c>
-      <c r="M27" s="6">
+      <c r="M27" s="5">
         <v>56340</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="O27" s="6">
+        <v>157</v>
+      </c>
+      <c r="O27" s="5">
         <v>46916</v>
       </c>
-      <c r="S27" s="3"/>
+      <c r="P27" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>97</v>
+        <v>158</v>
       </c>
       <c r="C28" s="2">
         <v>76381</v>
@@ -2811,13 +3024,13 @@
       <c r="E28" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>96</v>
+      <c r="F28" s="7" t="s">
+        <v>156</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H28" s="6">
+        <v>146</v>
+      </c>
+      <c r="H28" s="5">
         <v>45611</v>
       </c>
       <c r="I28" s="2">
@@ -2826,29 +3039,31 @@
       <c r="J28" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="5">
         <v>45200</v>
       </c>
-      <c r="L28" s="6">
+      <c r="L28" s="5">
         <v>36859</v>
       </c>
-      <c r="M28" s="6">
+      <c r="M28" s="5">
         <v>57315</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="O28" s="6">
+        <v>159</v>
+      </c>
+      <c r="O28" s="5">
         <v>47324</v>
       </c>
-      <c r="S28" s="3"/>
+      <c r="P28" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="C29" s="2">
         <v>77108</v>
@@ -2859,13 +3074,13 @@
       <c r="E29" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>99</v>
+      <c r="F29" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H29" s="6">
+        <v>146</v>
+      </c>
+      <c r="H29" s="5">
         <v>45915</v>
       </c>
       <c r="I29" s="2">
@@ -2874,29 +3089,31 @@
       <c r="J29" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="5">
         <v>45566</v>
       </c>
-      <c r="L29" s="6">
+      <c r="L29" s="5">
         <v>36036</v>
       </c>
-      <c r="M29" s="6">
+      <c r="M29" s="5">
         <v>56493</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="O29" s="6">
+        <v>162</v>
+      </c>
+      <c r="O29" s="5">
         <v>46944</v>
       </c>
-      <c r="S29" s="3"/>
+      <c r="P29" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>100</v>
+        <v>163</v>
       </c>
       <c r="C30" s="2">
         <v>76695</v>
@@ -2907,13 +3124,13 @@
       <c r="E30" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>96</v>
+      <c r="F30" s="7" t="s">
+        <v>156</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H30" s="6">
+        <v>146</v>
+      </c>
+      <c r="H30" s="5">
         <v>45658</v>
       </c>
       <c r="I30" s="2">
@@ -2922,29 +3139,31 @@
       <c r="J30" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K30" s="6">
+      <c r="K30" s="5">
         <v>45250</v>
       </c>
-      <c r="L30" s="6">
+      <c r="L30" s="5">
         <v>38497</v>
       </c>
-      <c r="M30" s="6">
+      <c r="M30" s="5">
         <v>58958</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="O30" s="6">
+        <v>164</v>
+      </c>
+      <c r="O30" s="5">
         <v>47324</v>
       </c>
-      <c r="S30" s="3"/>
+      <c r="P30" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="C31" s="2">
         <v>69673</v>
@@ -2955,14 +3174,14 @@
       <c r="E31" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>99</v>
+      <c r="F31" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H31" s="6">
-        <v>44927</v>
+        <v>146</v>
+      </c>
+      <c r="H31" s="5">
+        <v>43532</v>
       </c>
       <c r="I31" s="2">
         <v>5</v>
@@ -2970,29 +3189,31 @@
       <c r="J31" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K31" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L31" s="6">
+      <c r="K31" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L31" s="5">
         <v>33654</v>
       </c>
-      <c r="M31" s="6">
+      <c r="M31" s="5">
         <v>54118</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="O31" s="6">
+        <v>166</v>
+      </c>
+      <c r="O31" s="5">
         <v>46305</v>
       </c>
-      <c r="S31" s="3"/>
+      <c r="P31" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
       <c r="C32" s="2">
         <v>56345</v>
@@ -3003,14 +3224,14 @@
       <c r="E32" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>99</v>
+      <c r="F32" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H32" s="6">
-        <v>44927</v>
+        <v>146</v>
+      </c>
+      <c r="H32" s="5">
+        <v>43656</v>
       </c>
       <c r="I32" s="2">
         <v>5</v>
@@ -3018,29 +3239,31 @@
       <c r="J32" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K32" s="6">
+      <c r="K32" s="5">
         <v>40163</v>
       </c>
-      <c r="L32" s="6">
+      <c r="L32" s="5">
         <v>32677</v>
       </c>
-      <c r="M32" s="6">
+      <c r="M32" s="5">
         <v>53144</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="O32" s="6">
+        <v>168</v>
+      </c>
+      <c r="O32" s="5">
         <v>46861</v>
       </c>
-      <c r="S32" s="3"/>
+      <c r="P32" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="C33" s="2">
         <v>49888</v>
@@ -3051,14 +3274,14 @@
       <c r="E33" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>104</v>
+      <c r="F33" s="7" t="s">
+        <v>170</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H33" s="6">
-        <v>46023</v>
+        <v>171</v>
+      </c>
+      <c r="H33" s="5">
+        <v>45519</v>
       </c>
       <c r="I33" s="2">
         <v>8</v>
@@ -3066,28 +3289,31 @@
       <c r="J33" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K33" s="6">
+      <c r="K33" s="5">
         <v>39387</v>
       </c>
-      <c r="L33" s="6">
+      <c r="L33" s="5">
         <v>31650</v>
       </c>
-      <c r="M33" s="6">
+      <c r="M33" s="5">
         <v>52110</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="O33" s="6">
+        <v>172</v>
+      </c>
+      <c r="O33" s="5">
         <v>47261</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="C34" s="2">
         <v>53889</v>
@@ -3098,13 +3324,13 @@
       <c r="E34" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>107</v>
+      <c r="F34" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H34" s="6">
+        <v>171</v>
+      </c>
+      <c r="H34" s="5">
         <v>45093</v>
       </c>
       <c r="I34" s="2">
@@ -3113,23 +3339,31 @@
       <c r="J34" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K34" s="6">
+      <c r="K34" s="5">
         <v>39814</v>
       </c>
-      <c r="L34" s="6">
+      <c r="L34" s="5">
         <v>32935</v>
       </c>
-      <c r="M34" s="6">
+      <c r="M34" s="5">
         <v>53418</v>
       </c>
-      <c r="S34" s="3"/>
+      <c r="N34" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="O34" s="5">
+        <v>47265</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="35" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="C35" s="2">
         <v>53688</v>
@@ -3140,13 +3374,13 @@
       <c r="E35" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>109</v>
+      <c r="F35" s="7" t="s">
+        <v>177</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H35" s="6">
+        <v>171</v>
+      </c>
+      <c r="H35" s="5">
         <v>45717</v>
       </c>
       <c r="I35" s="2">
@@ -3155,29 +3389,31 @@
       <c r="J35" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K35" s="6">
+      <c r="K35" s="5">
         <v>39814</v>
       </c>
-      <c r="L35" s="6">
+      <c r="L35" s="5">
         <v>31924</v>
       </c>
-      <c r="M35" s="6">
+      <c r="M35" s="5">
         <v>52383</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="O35" s="6">
+        <v>178</v>
+      </c>
+      <c r="O35" s="5">
         <v>46953</v>
       </c>
-      <c r="S35" s="3"/>
+      <c r="P35" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="C36" s="2">
         <v>59724</v>
@@ -3188,14 +3424,14 @@
       <c r="E36" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>111</v>
+      <c r="F36" s="7" t="s">
+        <v>180</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H36" s="6">
-        <v>44927</v>
+        <v>171</v>
+      </c>
+      <c r="H36" s="5">
+        <v>42583</v>
       </c>
       <c r="I36" s="2">
         <v>5</v>
@@ -3203,29 +3439,31 @@
       <c r="J36" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K36" s="6">
-        <v>40545</v>
-      </c>
-      <c r="L36" s="6">
+      <c r="K36" s="5">
+        <v>40575</v>
+      </c>
+      <c r="L36" s="5">
         <v>32411</v>
       </c>
-      <c r="M36" s="6">
+      <c r="M36" s="5">
         <v>52871</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="O36" s="6">
+        <v>181</v>
+      </c>
+      <c r="O36" s="5">
         <v>46837</v>
       </c>
-      <c r="S36" s="3"/>
+      <c r="P36" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>112</v>
+        <v>182</v>
       </c>
       <c r="C37" s="2">
         <v>71501</v>
@@ -3236,14 +3474,14 @@
       <c r="E37" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>111</v>
+      <c r="F37" s="7" t="s">
+        <v>180</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H37" s="6">
-        <v>44927</v>
+        <v>171</v>
+      </c>
+      <c r="H37" s="5">
+        <v>43375</v>
       </c>
       <c r="I37" s="2">
         <v>5</v>
@@ -3251,29 +3489,31 @@
       <c r="J37" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K37" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L37" s="6">
+      <c r="K37" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L37" s="5">
         <v>34525</v>
       </c>
-      <c r="M37" s="6">
+      <c r="M37" s="5">
         <v>55001</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="O37" s="6">
+        <v>183</v>
+      </c>
+      <c r="O37" s="5">
         <v>46259</v>
       </c>
-      <c r="S37" s="3"/>
+      <c r="P37" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>113</v>
+        <v>184</v>
       </c>
       <c r="C38" s="2">
         <v>56304</v>
@@ -3284,14 +3524,14 @@
       <c r="E38" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>114</v>
+      <c r="F38" s="7" t="s">
+        <v>185</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H38" s="6">
-        <v>44927</v>
+        <v>171</v>
+      </c>
+      <c r="H38" s="5">
+        <v>44091</v>
       </c>
       <c r="I38" s="2">
         <v>5</v>
@@ -3299,29 +3539,31 @@
       <c r="J38" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K38" s="6">
+      <c r="K38" s="5">
         <v>40163</v>
       </c>
-      <c r="L38" s="6">
+      <c r="L38" s="5">
         <v>32677</v>
       </c>
-      <c r="M38" s="6">
-        <v>53144</v>
+      <c r="M38" s="5">
+        <v>52536</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="O38" s="6">
+        <v>186</v>
+      </c>
+      <c r="O38" s="5">
         <v>46837</v>
       </c>
-      <c r="S38" s="3"/>
+      <c r="P38" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>115</v>
+        <v>187</v>
       </c>
       <c r="C39" s="2">
         <v>69666</v>
@@ -3332,14 +3574,14 @@
       <c r="E39" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F39" s="4" t="s">
-        <v>114</v>
+      <c r="F39" s="7" t="s">
+        <v>185</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H39" s="6">
-        <v>44927</v>
+        <v>171</v>
+      </c>
+      <c r="H39" s="5">
+        <v>44091</v>
       </c>
       <c r="I39" s="2">
         <v>5</v>
@@ -3347,28 +3589,31 @@
       <c r="J39" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K39" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L39" s="6">
-        <v>33953</v>
-      </c>
-      <c r="M39" s="6">
-        <v>54424</v>
+      <c r="K39" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L39" s="5">
+        <v>34106</v>
+      </c>
+      <c r="M39" s="5">
+        <v>54575</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="O39" s="6">
+        <v>188</v>
+      </c>
+      <c r="O39" s="5">
         <v>46259</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>116</v>
+        <v>189</v>
       </c>
       <c r="C40" s="2">
         <v>75387</v>
@@ -3379,13 +3624,13 @@
       <c r="E40" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>114</v>
+      <c r="F40" s="7" t="s">
+        <v>185</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H40" s="6">
+        <v>171</v>
+      </c>
+      <c r="H40" s="5">
         <v>45717</v>
       </c>
       <c r="I40" s="2">
@@ -3394,29 +3639,31 @@
       <c r="J40" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K40" s="6">
+      <c r="K40" s="5">
         <v>44958</v>
       </c>
-      <c r="L40" s="6">
+      <c r="L40" s="5">
         <v>37714</v>
       </c>
-      <c r="M40" s="6">
+      <c r="M40" s="5">
         <v>58196</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="O40" s="6">
+        <v>190</v>
+      </c>
+      <c r="O40" s="5">
         <v>47370</v>
       </c>
-      <c r="S40" s="3"/>
+      <c r="P40" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>117</v>
+        <v>191</v>
       </c>
       <c r="C41" s="2">
         <v>46479</v>
@@ -3427,14 +3674,14 @@
       <c r="E41" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>118</v>
+      <c r="F41" s="7" t="s">
+        <v>192</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H41" s="6">
-        <v>44927</v>
+        <v>193</v>
+      </c>
+      <c r="H41" s="5">
+        <v>44883</v>
       </c>
       <c r="I41" s="2">
         <v>8</v>
@@ -3442,35 +3689,40 @@
       <c r="J41" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K41" s="6">
-        <v>35433</v>
-      </c>
-      <c r="L41" s="6">
+      <c r="K41" s="5">
+        <v>35490</v>
+      </c>
+      <c r="L41" s="5">
         <v>28092</v>
       </c>
-      <c r="M41" s="6">
+      <c r="M41" s="5">
         <v>48549</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="O41" s="6">
+        <v>194</v>
+      </c>
+      <c r="O41" s="5">
         <v>47285</v>
       </c>
+      <c r="P41" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q41" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="R41" s="6">
+        <v>195</v>
+      </c>
+      <c r="R41" s="5">
         <v>47110</v>
       </c>
-      <c r="S41" s="3"/>
+      <c r="S41" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="42" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>120</v>
+        <v>196</v>
       </c>
       <c r="C42" s="2">
         <v>59095</v>
@@ -3481,13 +3733,13 @@
       <c r="E42" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>121</v>
+      <c r="F42" s="7" t="s">
+        <v>197</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H42" s="6">
+        <v>193</v>
+      </c>
+      <c r="H42" s="5">
         <v>45703</v>
       </c>
       <c r="I42" s="2">
@@ -3496,29 +3748,31 @@
       <c r="J42" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K42" s="6">
+      <c r="K42" s="5">
         <v>40575</v>
       </c>
-      <c r="L42" s="6">
-        <v>30796</v>
-      </c>
-      <c r="M42" s="6">
+      <c r="L42" s="5">
+        <v>30783</v>
+      </c>
+      <c r="M42" s="5">
         <v>51257</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="O42" s="6">
+        <v>198</v>
+      </c>
+      <c r="O42" s="5">
         <v>47203</v>
       </c>
-      <c r="S42" s="3"/>
+      <c r="P42" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="43" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>122</v>
+        <v>199</v>
       </c>
       <c r="C43" s="2">
         <v>53944</v>
@@ -3529,14 +3783,14 @@
       <c r="E43" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>123</v>
+      <c r="F43" s="7" t="s">
+        <v>200</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H43" s="6">
-        <v>44927</v>
+        <v>193</v>
+      </c>
+      <c r="H43" s="5">
+        <v>44883</v>
       </c>
       <c r="I43" s="2">
         <v>7</v>
@@ -3544,29 +3798,31 @@
       <c r="J43" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K43" s="6">
+      <c r="K43" s="5">
         <v>39814</v>
       </c>
-      <c r="L43" s="6">
+      <c r="L43" s="5">
         <v>33105</v>
       </c>
-      <c r="M43" s="6">
+      <c r="M43" s="5">
         <v>53571</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="O43" s="6">
+        <v>201</v>
+      </c>
+      <c r="O43" s="5">
         <v>47005</v>
       </c>
-      <c r="S43" s="3"/>
+      <c r="P43" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>124</v>
+        <v>202</v>
       </c>
       <c r="C44" s="2">
         <v>69105</v>
@@ -3577,14 +3833,14 @@
       <c r="E44" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>125</v>
+      <c r="F44" s="7" t="s">
+        <v>203</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H44" s="6">
-        <v>44927</v>
+        <v>193</v>
+      </c>
+      <c r="H44" s="5">
+        <v>43164</v>
       </c>
       <c r="I44" s="2">
         <v>5</v>
@@ -3592,29 +3848,31 @@
       <c r="J44" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K44" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L44" s="6">
+      <c r="K44" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L44" s="5">
         <v>32276</v>
       </c>
-      <c r="M44" s="6">
+      <c r="M44" s="5">
         <v>52749</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="O44" s="6">
+        <v>204</v>
+      </c>
+      <c r="O44" s="5">
         <v>46305</v>
       </c>
-      <c r="S44" s="3"/>
+      <c r="P44" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>126</v>
+        <v>205</v>
       </c>
       <c r="C45" s="2">
         <v>74708</v>
@@ -3625,13 +3883,13 @@
       <c r="E45" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F45" s="4" t="s">
-        <v>125</v>
+      <c r="F45" s="7" t="s">
+        <v>203</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H45" s="6">
+        <v>193</v>
+      </c>
+      <c r="H45" s="5">
         <v>45717</v>
       </c>
       <c r="I45" s="2">
@@ -3640,22 +3898,31 @@
       <c r="J45" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K45" s="6">
+      <c r="K45" s="5">
         <v>44866</v>
       </c>
-      <c r="L45" s="6">
+      <c r="L45" s="5">
         <v>37352</v>
       </c>
-      <c r="M45" s="6">
+      <c r="M45" s="5">
         <v>57831</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="O45" s="5">
+        <v>46851</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>127</v>
+        <v>207</v>
       </c>
       <c r="C46" s="2">
         <v>75398</v>
@@ -3666,13 +3933,13 @@
       <c r="E46" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F46" s="4" t="s">
-        <v>125</v>
+      <c r="F46" s="7" t="s">
+        <v>203</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H46" s="6">
+        <v>193</v>
+      </c>
+      <c r="H46" s="5">
         <v>45566</v>
       </c>
       <c r="I46" s="2">
@@ -3681,29 +3948,31 @@
       <c r="J46" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K46" s="6">
+      <c r="K46" s="5">
         <v>44958</v>
       </c>
-      <c r="L46" s="6">
+      <c r="L46" s="5">
         <v>37494</v>
       </c>
-      <c r="M46" s="6">
+      <c r="M46" s="5">
         <v>57954</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="O46" s="6">
+        <v>208</v>
+      </c>
+      <c r="O46" s="5">
         <v>47324</v>
       </c>
-      <c r="S46" s="3"/>
+      <c r="P46" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>128</v>
+        <v>209</v>
       </c>
       <c r="C47" s="2">
         <v>69170</v>
@@ -3714,14 +3983,14 @@
       <c r="E47" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F47" s="4" t="s">
-        <v>129</v>
+      <c r="F47" s="7" t="s">
+        <v>210</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H47" s="6">
-        <v>44927</v>
+        <v>193</v>
+      </c>
+      <c r="H47" s="5">
+        <v>43846</v>
       </c>
       <c r="I47" s="2">
         <v>5</v>
@@ -3729,23 +3998,31 @@
       <c r="J47" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K47" s="6">
+      <c r="K47" s="5">
         <v>42562</v>
       </c>
-      <c r="L47" s="6">
+      <c r="L47" s="5">
         <v>34653</v>
       </c>
-      <c r="M47" s="6">
+      <c r="M47" s="5">
         <v>55123</v>
       </c>
-      <c r="S47" s="3"/>
+      <c r="N47" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="O47" s="5">
+        <v>46305</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>130</v>
+        <v>212</v>
       </c>
       <c r="C48" s="2">
         <v>71482</v>
@@ -3756,14 +4033,14 @@
       <c r="E48" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F48" s="4" t="s">
-        <v>129</v>
+      <c r="F48" s="7" t="s">
+        <v>210</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H48" s="6">
-        <v>44927</v>
+        <v>193</v>
+      </c>
+      <c r="H48" s="5">
+        <v>44091</v>
       </c>
       <c r="I48" s="2">
         <v>5</v>
@@ -3771,29 +4048,31 @@
       <c r="J48" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K48" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L48" s="6">
+      <c r="K48" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L48" s="5">
         <v>35028</v>
       </c>
-      <c r="M48" s="6">
+      <c r="M48" s="5">
         <v>55488</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="O48" s="6">
+        <v>213</v>
+      </c>
+      <c r="O48" s="5">
         <v>46305</v>
       </c>
-      <c r="S48" s="3"/>
+      <c r="P48" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>131</v>
+        <v>214</v>
       </c>
       <c r="C49" s="2">
         <v>76912</v>
@@ -3804,13 +4083,13 @@
       <c r="E49" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F49" s="4" t="s">
-        <v>129</v>
+      <c r="F49" s="7" t="s">
+        <v>210</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H49" s="6">
+        <v>193</v>
+      </c>
+      <c r="H49" s="5">
         <v>45658</v>
       </c>
       <c r="I49" s="2">
@@ -3819,29 +4098,31 @@
       <c r="J49" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K49" s="6">
+      <c r="K49" s="5">
         <v>45289</v>
       </c>
-      <c r="L49" s="6">
+      <c r="L49" s="5">
         <v>37269</v>
       </c>
-      <c r="M49" s="6">
+      <c r="M49" s="5">
         <v>57742</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="O49" s="6">
+        <v>215</v>
+      </c>
+      <c r="O49" s="5">
         <v>47295</v>
       </c>
-      <c r="S49" s="3"/>
+      <c r="P49" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>132</v>
+        <v>216</v>
       </c>
       <c r="C50" s="2">
         <v>43394</v>
@@ -3852,13 +4133,13 @@
       <c r="E50" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F50" s="4" t="s">
-        <v>133</v>
+      <c r="F50" s="7" t="s">
+        <v>217</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H50" s="6">
+        <v>218</v>
+      </c>
+      <c r="H50" s="5">
         <v>45566</v>
       </c>
       <c r="I50" s="2">
@@ -3867,35 +4148,40 @@
       <c r="J50" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K50" s="6">
+      <c r="K50" s="5">
         <v>35217</v>
       </c>
-      <c r="L50" s="6">
-        <v>27536</v>
-      </c>
-      <c r="M50" s="6">
+      <c r="L50" s="5">
+        <v>27350</v>
+      </c>
+      <c r="M50" s="5">
         <v>48000</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="O50" s="6">
+        <v>219</v>
+      </c>
+      <c r="O50" s="5">
         <v>47054</v>
       </c>
+      <c r="P50" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q50" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="R50" s="6">
+        <v>220</v>
+      </c>
+      <c r="R50" s="5">
         <v>47285</v>
       </c>
-      <c r="S50" s="3"/>
+      <c r="S50" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="51" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>135</v>
+        <v>221</v>
       </c>
       <c r="C51" s="2">
         <v>53854</v>
@@ -3906,13 +4192,13 @@
       <c r="E51" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F51" s="4" t="s">
-        <v>136</v>
+      <c r="F51" s="7" t="s">
+        <v>222</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H51" s="6">
+        <v>218</v>
+      </c>
+      <c r="H51" s="5">
         <v>45717</v>
       </c>
       <c r="I51" s="2">
@@ -3921,29 +4207,31 @@
       <c r="J51" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K51" s="6">
+      <c r="K51" s="5">
         <v>39814</v>
       </c>
-      <c r="L51" s="6">
+      <c r="L51" s="5">
         <v>32825</v>
       </c>
-      <c r="M51" s="6">
+      <c r="M51" s="5">
         <v>53297</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="O51" s="6">
+        <v>223</v>
+      </c>
+      <c r="O51" s="5">
         <v>47054</v>
       </c>
-      <c r="S51" s="3"/>
+      <c r="P51" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="52" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>137</v>
+        <v>224</v>
       </c>
       <c r="C52" s="2">
         <v>56356</v>
@@ -3954,13 +4242,13 @@
       <c r="E52" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F52" s="4" t="s">
-        <v>138</v>
+      <c r="F52" s="7" t="s">
+        <v>225</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H52" s="6">
+        <v>218</v>
+      </c>
+      <c r="H52" s="5">
         <v>45519</v>
       </c>
       <c r="I52" s="2">
@@ -3969,30 +4257,31 @@
       <c r="J52" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K52" s="6">
+      <c r="K52" s="5">
         <v>40163</v>
       </c>
-      <c r="L52" s="6">
+      <c r="L52" s="5">
         <v>33500</v>
       </c>
-      <c r="M52" s="6">
+      <c r="M52" s="5">
         <v>53966</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="O52" s="6">
+        <v>226</v>
+      </c>
+      <c r="O52" s="5">
         <v>46937</v>
       </c>
-      <c r="P52" s="3"/>
-      <c r="S52" s="3"/>
+      <c r="P52" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>139</v>
+        <v>227</v>
       </c>
       <c r="C53" s="2">
         <v>62165</v>
@@ -4003,14 +4292,14 @@
       <c r="E53" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F53" s="4" t="s">
-        <v>140</v>
+      <c r="F53" s="7" t="s">
+        <v>228</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H53" s="6">
-        <v>44927</v>
+        <v>218</v>
+      </c>
+      <c r="H53" s="5">
+        <v>43235</v>
       </c>
       <c r="I53" s="2">
         <v>5</v>
@@ -4018,30 +4307,31 @@
       <c r="J53" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K53" s="6">
-        <v>40917</v>
-      </c>
-      <c r="L53" s="6">
+      <c r="K53" s="5">
+        <v>41153</v>
+      </c>
+      <c r="L53" s="5">
         <v>32442</v>
       </c>
-      <c r="M53" s="6">
+      <c r="M53" s="5">
         <v>52902</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="O53" s="6">
+        <v>229</v>
+      </c>
+      <c r="O53" s="5">
         <v>46851</v>
       </c>
-      <c r="P53" s="3"/>
-      <c r="S53" s="3"/>
+      <c r="P53" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>141</v>
+        <v>230</v>
       </c>
       <c r="C54" s="2">
         <v>69994</v>
@@ -4052,14 +4342,14 @@
       <c r="E54" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F54" s="4" t="s">
-        <v>140</v>
+      <c r="F54" s="7" t="s">
+        <v>228</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H54" s="6">
-        <v>44927</v>
+        <v>218</v>
+      </c>
+      <c r="H54" s="5">
+        <v>43846</v>
       </c>
       <c r="I54" s="2">
         <v>5</v>
@@ -4067,24 +4357,31 @@
       <c r="J54" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K54" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L54" s="6">
+      <c r="K54" s="5">
+        <v>42597</v>
+      </c>
+      <c r="L54" s="5">
         <v>34422</v>
       </c>
-      <c r="M54" s="6">
+      <c r="M54" s="5">
         <v>54879</v>
       </c>
-      <c r="P54" s="3"/>
-      <c r="S54" s="3"/>
+      <c r="N54" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="O54" s="5">
+        <v>46305</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>142</v>
+        <v>232</v>
       </c>
       <c r="C55" s="2">
         <v>69993</v>
@@ -4095,14 +4392,14 @@
       <c r="E55" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F55" s="4" t="s">
-        <v>143</v>
+      <c r="F55" s="7" t="s">
+        <v>233</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H55" s="6">
-        <v>44927</v>
+        <v>218</v>
+      </c>
+      <c r="H55" s="5">
+        <v>43656</v>
       </c>
       <c r="I55" s="2">
         <v>5</v>
@@ -4110,30 +4407,31 @@
       <c r="J55" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K55" s="6">
+      <c r="K55" s="5">
         <v>42597</v>
       </c>
-      <c r="L55" s="6">
+      <c r="L55" s="5">
         <v>34541</v>
       </c>
-      <c r="M55" s="6">
+      <c r="M55" s="5">
         <v>55001</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="O55" s="6">
+        <v>234</v>
+      </c>
+      <c r="O55" s="5">
         <v>46305</v>
       </c>
-      <c r="P55" s="3"/>
-      <c r="S55" s="3"/>
+      <c r="P55" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A56" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>144</v>
+        <v>235</v>
       </c>
       <c r="C56" s="2">
         <v>69149</v>
@@ -4144,13 +4442,13 @@
       <c r="E56" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F56" s="4" t="s">
-        <v>143</v>
+      <c r="F56" s="7" t="s">
+        <v>233</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H56" s="6">
+        <v>218</v>
+      </c>
+      <c r="H56" s="5">
         <v>45444</v>
       </c>
       <c r="I56" s="2">
@@ -4159,30 +4457,31 @@
       <c r="J56" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K56" s="6">
+      <c r="K56" s="5">
         <v>42562</v>
       </c>
-      <c r="L56" s="6">
+      <c r="L56" s="5">
         <v>32748</v>
       </c>
-      <c r="M56" s="6">
+      <c r="M56" s="5">
         <v>53206</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="O56" s="6">
+        <v>236</v>
+      </c>
+      <c r="O56" s="5">
         <v>46305</v>
       </c>
-      <c r="P56" s="3"/>
-      <c r="S56" s="3"/>
+      <c r="P56" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>145</v>
+        <v>237</v>
       </c>
       <c r="C57" s="2">
         <v>46335</v>
@@ -4193,13 +4492,13 @@
       <c r="E57" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F57" s="4" t="s">
-        <v>146</v>
+      <c r="F57" s="7" t="s">
+        <v>238</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H57" s="6">
+        <v>239</v>
+      </c>
+      <c r="H57" s="5">
         <v>45992</v>
       </c>
       <c r="I57" s="2">
@@ -4208,24 +4507,31 @@
       <c r="J57" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K57" s="6">
-        <v>35433</v>
-      </c>
-      <c r="L57" s="6">
+      <c r="K57" s="5">
+        <v>35490</v>
+      </c>
+      <c r="L57" s="5">
         <v>28547</v>
       </c>
-      <c r="M57" s="6">
+      <c r="M57" s="5">
         <v>49004</v>
       </c>
-      <c r="P57" s="3"/>
-      <c r="S57" s="3"/>
+      <c r="N57" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="O57" s="5">
+        <v>47265</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="58" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>148</v>
+        <v>241</v>
       </c>
       <c r="C58" s="2">
         <v>56319</v>
@@ -4236,13 +4542,13 @@
       <c r="E58" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F58" s="4" t="s">
-        <v>149</v>
+      <c r="F58" s="7" t="s">
+        <v>242</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H58" s="6">
+        <v>239</v>
+      </c>
+      <c r="H58" s="5">
         <v>45519</v>
       </c>
       <c r="I58" s="2">
@@ -4251,24 +4557,31 @@
       <c r="J58" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K58" s="6">
+      <c r="K58" s="5">
         <v>40163</v>
       </c>
-      <c r="L58" s="6">
+      <c r="L58" s="5">
         <v>31928</v>
       </c>
-      <c r="M58" s="6">
+      <c r="M58" s="5">
         <v>52383</v>
       </c>
-      <c r="P58" s="3"/>
-      <c r="S58" s="3"/>
+      <c r="N58" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="O58" s="5">
+        <v>46972</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="59" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>150</v>
+        <v>244</v>
       </c>
       <c r="C59" s="2">
         <v>53697</v>
@@ -4279,14 +4592,14 @@
       <c r="E59" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F59" s="4" t="s">
-        <v>151</v>
+      <c r="F59" s="7" t="s">
+        <v>245</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H59" s="6">
-        <v>46023</v>
+        <v>239</v>
+      </c>
+      <c r="H59" s="5">
+        <v>45093</v>
       </c>
       <c r="I59" s="2">
         <v>8</v>
@@ -4294,24 +4607,31 @@
       <c r="J59" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K59" s="6">
+      <c r="K59" s="5">
         <v>39814</v>
       </c>
-      <c r="L59" s="6">
+      <c r="L59" s="5">
         <v>32125</v>
       </c>
-      <c r="M59" s="6">
+      <c r="M59" s="5">
         <v>52597</v>
       </c>
-      <c r="P59" s="3"/>
-      <c r="S59" s="3"/>
+      <c r="N59" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="O59" s="5">
+        <v>47265</v>
+      </c>
+      <c r="P59" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>152</v>
+        <v>247</v>
       </c>
       <c r="C60" s="2">
         <v>74487</v>
@@ -4322,13 +4642,13 @@
       <c r="E60" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F60" s="4" t="s">
-        <v>153</v>
+      <c r="F60" s="7" t="s">
+        <v>248</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H60" s="6">
+        <v>239</v>
+      </c>
+      <c r="H60" s="5">
         <v>45717</v>
       </c>
       <c r="I60" s="2">
@@ -4337,30 +4657,31 @@
       <c r="J60" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K60" s="6">
+      <c r="K60" s="5">
         <v>44816</v>
       </c>
-      <c r="L60" s="6">
+      <c r="L60" s="5">
         <v>37464</v>
       </c>
-      <c r="M60" s="6">
+      <c r="M60" s="5">
         <v>57923</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="O60" s="6">
+        <v>249</v>
+      </c>
+      <c r="O60" s="5">
         <v>46727</v>
       </c>
-      <c r="P60" s="3"/>
-      <c r="S60" s="3"/>
+      <c r="P60" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>154</v>
+        <v>250</v>
       </c>
       <c r="C61" s="2">
         <v>61477</v>
@@ -4371,14 +4692,14 @@
       <c r="E61" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F61" s="4" t="s">
-        <v>153</v>
+      <c r="F61" s="7" t="s">
+        <v>248</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H61" s="6">
-        <v>44927</v>
+        <v>239</v>
+      </c>
+      <c r="H61" s="5">
+        <v>43235</v>
       </c>
       <c r="I61" s="2">
         <v>5</v>
@@ -4386,24 +4707,31 @@
       <c r="J61" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K61" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L61" s="6">
+      <c r="K61" s="5">
+        <v>40787</v>
+      </c>
+      <c r="L61" s="5">
         <v>34094</v>
       </c>
-      <c r="M61" s="6">
+      <c r="M61" s="5">
         <v>54575</v>
       </c>
-      <c r="P61" s="3"/>
-      <c r="S61" s="3"/>
+      <c r="N61" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="O61" s="5">
+        <v>46851</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="C62" s="2">
         <v>69997</v>
@@ -4414,14 +4742,14 @@
       <c r="E62" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F62" s="4" t="s">
-        <v>153</v>
+      <c r="F62" s="7" t="s">
+        <v>248</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H62" s="6">
-        <v>44927</v>
+        <v>239</v>
+      </c>
+      <c r="H62" s="5">
+        <v>44091</v>
       </c>
       <c r="I62" s="2">
         <v>5</v>
@@ -4429,30 +4757,31 @@
       <c r="J62" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K62" s="6">
-        <v>39814</v>
-      </c>
-      <c r="L62" s="6">
+      <c r="K62" s="5">
+        <v>42597</v>
+      </c>
+      <c r="L62" s="5">
         <v>33868</v>
       </c>
-      <c r="M62" s="6">
-        <v>54332</v>
+      <c r="M62" s="5">
+        <v>53783</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="O62" s="6">
+        <v>253</v>
+      </c>
+      <c r="O62" s="5">
         <v>46433</v>
       </c>
-      <c r="P62" s="3"/>
-      <c r="S62" s="3"/>
+      <c r="P62" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>156</v>
+        <v>254</v>
       </c>
       <c r="C63" s="2">
         <v>61483</v>
@@ -4463,14 +4792,14 @@
       <c r="E63" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F63" s="4" t="s">
-        <v>153</v>
+      <c r="F63" s="7" t="s">
+        <v>248</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H63" s="6">
-        <v>44927</v>
+        <v>239</v>
+      </c>
+      <c r="H63" s="5">
+        <v>44441</v>
       </c>
       <c r="I63" s="2">
         <v>5</v>
@@ -4478,30 +4807,31 @@
       <c r="J63" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K63" s="6">
-        <v>40552</v>
-      </c>
-      <c r="L63" s="6">
+      <c r="K63" s="5">
+        <v>40787</v>
+      </c>
+      <c r="L63" s="5">
         <v>34163</v>
       </c>
-      <c r="M63" s="6">
+      <c r="M63" s="5">
         <v>54636</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="O63" s="6">
+        <v>255</v>
+      </c>
+      <c r="O63" s="5">
         <v>46851</v>
       </c>
-      <c r="P63" s="3"/>
-      <c r="S63" s="3"/>
+      <c r="P63" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>157</v>
+        <v>256</v>
       </c>
       <c r="C64" s="2">
         <v>69068</v>
@@ -4512,14 +4842,14 @@
       <c r="E64" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F64" s="4" t="s">
-        <v>158</v>
+      <c r="F64" s="7" t="s">
+        <v>257</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H64" s="6">
-        <v>44927</v>
+        <v>239</v>
+      </c>
+      <c r="H64" s="5">
+        <v>43656</v>
       </c>
       <c r="I64" s="2">
         <v>5</v>
@@ -4527,24 +4857,31 @@
       <c r="J64" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K64" s="6">
-        <v>40552</v>
-      </c>
-      <c r="L64" s="6">
+      <c r="K64" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L64" s="5">
         <v>35225</v>
       </c>
-      <c r="M64" s="6">
+      <c r="M64" s="5">
         <v>55701</v>
       </c>
-      <c r="P64" s="3"/>
-      <c r="S64" s="3"/>
+      <c r="N64" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="O64" s="5">
+        <v>46263</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>159</v>
+        <v>259</v>
       </c>
       <c r="C65" s="2">
         <v>61484</v>
@@ -4555,14 +4892,14 @@
       <c r="E65" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F65" s="4" t="s">
-        <v>158</v>
+      <c r="F65" s="7" t="s">
+        <v>257</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H65" s="6">
-        <v>44927</v>
+        <v>239</v>
+      </c>
+      <c r="H65" s="5">
+        <v>43532</v>
       </c>
       <c r="I65" s="2">
         <v>5</v>
@@ -4570,30 +4907,31 @@
       <c r="J65" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K65" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L65" s="6">
+      <c r="K65" s="5">
+        <v>40787</v>
+      </c>
+      <c r="L65" s="5">
         <v>34166</v>
       </c>
-      <c r="M65" s="6">
+      <c r="M65" s="5">
         <v>54636</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="O65" s="6">
+        <v>260</v>
+      </c>
+      <c r="O65" s="5">
         <v>46851</v>
       </c>
-      <c r="P65" s="3"/>
-      <c r="S65" s="3"/>
+      <c r="P65" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>160</v>
+        <v>261</v>
       </c>
       <c r="C66" s="2">
         <v>75875</v>
@@ -4604,13 +4942,13 @@
       <c r="E66" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F66" s="4" t="s">
-        <v>158</v>
+      <c r="F66" s="7" t="s">
+        <v>257</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H66" s="6">
+        <v>239</v>
+      </c>
+      <c r="H66" s="5">
         <v>45839</v>
       </c>
       <c r="I66" s="2">
@@ -4619,30 +4957,31 @@
       <c r="J66" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K66" s="6">
+      <c r="K66" s="5">
         <v>45047</v>
       </c>
-      <c r="L66" s="6">
+      <c r="L66" s="5">
         <v>37452</v>
       </c>
-      <c r="M66" s="6">
+      <c r="M66" s="5">
         <v>57923</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="O66" s="6">
+        <v>262</v>
+      </c>
+      <c r="O66" s="5">
         <v>47285</v>
       </c>
-      <c r="P66" s="3"/>
-      <c r="S66" s="3"/>
+      <c r="P66" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>161</v>
+        <v>263</v>
       </c>
       <c r="C67" s="2">
         <v>74689</v>
@@ -4653,13 +4992,13 @@
       <c r="E67" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F67" s="4" t="s">
-        <v>158</v>
+      <c r="F67" s="7" t="s">
+        <v>257</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H67" s="6">
+        <v>239</v>
+      </c>
+      <c r="H67" s="5">
         <v>45176</v>
       </c>
       <c r="I67" s="2">
@@ -4668,24 +5007,31 @@
       <c r="J67" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K67" s="6">
+      <c r="K67" s="5">
         <v>44866</v>
       </c>
-      <c r="L67" s="6">
+      <c r="L67" s="5">
         <v>36623</v>
       </c>
-      <c r="M67" s="6">
+      <c r="M67" s="5">
         <v>57101</v>
       </c>
-      <c r="P67" s="3"/>
-      <c r="S67" s="3"/>
+      <c r="N67" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="O67" s="5">
+        <v>46851</v>
+      </c>
+      <c r="P67" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>162</v>
+        <v>265</v>
       </c>
       <c r="C68" s="2">
         <v>50026</v>
@@ -4696,14 +5042,14 @@
       <c r="E68" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F68" s="4" t="s">
-        <v>163</v>
+      <c r="F68" s="7" t="s">
+        <v>266</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="H68" s="6">
-        <v>44927</v>
+        <v>267</v>
+      </c>
+      <c r="H68" s="5">
+        <v>44440</v>
       </c>
       <c r="I68" s="2">
         <v>8</v>
@@ -4711,41 +5057,57 @@
       <c r="J68" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K68" s="6">
+      <c r="K68" s="5">
         <v>39387</v>
       </c>
-      <c r="L68" s="6">
+      <c r="L68" s="5">
         <v>32088</v>
       </c>
-      <c r="M68" s="6">
-        <v>52566</v>
-      </c>
-      <c r="P68" s="3"/>
-      <c r="S68" s="3"/>
+      <c r="M68" s="5">
+        <v>52444</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="O68" s="5">
+        <v>47054</v>
+      </c>
+      <c r="P68" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q68" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="R68" s="5">
+        <v>47097</v>
+      </c>
+      <c r="S68" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="69" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>165</v>
+        <v>270</v>
       </c>
       <c r="C69" s="2">
         <v>53687</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D69" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F69" s="4" t="s">
-        <v>166</v>
+      <c r="F69" s="7" t="s">
+        <v>271</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="H69" s="8">
+        <v>267</v>
+      </c>
+      <c r="H69" s="5">
         <v>45717</v>
       </c>
       <c r="I69" s="2">
@@ -4754,42 +5116,49 @@
       <c r="J69" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K69" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L69" s="6">
+      <c r="K69" s="5">
+        <v>39814</v>
+      </c>
+      <c r="L69" s="5">
         <v>31920</v>
       </c>
-      <c r="M69" s="6">
+      <c r="M69" s="5">
         <v>52383</v>
       </c>
-      <c r="P69" s="3"/>
-      <c r="S69" s="3"/>
+      <c r="N69" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="O69" s="5">
+        <v>47261</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="70" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>167</v>
+        <v>273</v>
       </c>
       <c r="C70" s="2">
         <v>53678</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D70" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F70" s="4" t="s">
-        <v>168</v>
+      <c r="F70" s="7" t="s">
+        <v>274</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="H70" s="8">
-        <v>44927</v>
+        <v>267</v>
+      </c>
+      <c r="H70" s="5">
+        <v>44348</v>
       </c>
       <c r="I70" s="2">
         <v>7</v>
@@ -4797,48 +5166,49 @@
       <c r="J70" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K70" s="6">
+      <c r="K70" s="5">
         <v>39814</v>
       </c>
-      <c r="L70" s="6">
+      <c r="L70" s="5">
         <v>31719</v>
       </c>
-      <c r="M70" s="6">
+      <c r="M70" s="5">
         <v>52201</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="O70" s="6">
+        <v>275</v>
+      </c>
+      <c r="O70" s="5">
         <v>47005</v>
       </c>
-      <c r="P70" s="3"/>
-      <c r="S70" s="3"/>
+      <c r="P70" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>169</v>
+        <v>276</v>
       </c>
       <c r="C71" s="2">
         <v>69096</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F71" s="4" t="s">
-        <v>170</v>
+      <c r="F71" s="7" t="s">
+        <v>277</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="H71" s="6">
-        <v>44927</v>
+        <v>267</v>
+      </c>
+      <c r="H71" s="5">
+        <v>43420</v>
       </c>
       <c r="I71" s="2">
         <v>5</v>
@@ -4846,47 +5216,48 @@
       <c r="J71" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K71" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L71" s="6">
+      <c r="K71" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L71" s="5">
         <v>33240</v>
       </c>
-      <c r="M71" s="6">
-        <v>53724</v>
+      <c r="M71" s="5">
+        <v>53997</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="O71" s="6">
+        <v>278</v>
+      </c>
+      <c r="O71" s="5">
         <v>46259</v>
       </c>
-      <c r="P71" s="3"/>
-      <c r="S71" s="3"/>
+      <c r="P71" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>171</v>
+        <v>279</v>
       </c>
       <c r="C72" s="2">
         <v>69094</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F72" s="4" t="s">
-        <v>170</v>
+      <c r="F72" s="7" t="s">
+        <v>277</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="H72" s="8">
+        <v>267</v>
+      </c>
+      <c r="H72" s="5">
         <v>45444</v>
       </c>
       <c r="I72" s="2">
@@ -4895,47 +5266,48 @@
       <c r="J72" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K72" s="6">
+      <c r="K72" s="5">
         <v>42562</v>
       </c>
-      <c r="L72" s="6">
+      <c r="L72" s="5">
         <v>32440</v>
       </c>
-      <c r="M72" s="6">
+      <c r="M72" s="5">
         <v>52902</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="O72" s="6">
+        <v>280</v>
+      </c>
+      <c r="O72" s="5">
         <v>46305</v>
       </c>
-      <c r="P72" s="3"/>
-      <c r="S72" s="3"/>
+      <c r="P72" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A73" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>172</v>
+        <v>281</v>
       </c>
       <c r="C73" s="2">
         <v>75392</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F73" s="4" t="s">
-        <v>170</v>
+      <c r="F73" s="7" t="s">
+        <v>277</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="H73" s="8">
+        <v>267</v>
+      </c>
+      <c r="H73" s="5">
         <v>45536</v>
       </c>
       <c r="I73" s="2">
@@ -4944,48 +5316,49 @@
       <c r="J73" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K73" s="6">
+      <c r="K73" s="5">
         <v>44958</v>
       </c>
-      <c r="L73" s="6">
+      <c r="L73" s="5">
         <v>36533</v>
       </c>
-      <c r="M73" s="6">
+      <c r="M73" s="5">
         <v>57011</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="O73" s="6">
+        <v>282</v>
+      </c>
+      <c r="O73" s="5">
         <v>47110</v>
       </c>
-      <c r="P73" s="3"/>
-      <c r="S73" s="3"/>
+      <c r="P73" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>173</v>
+        <v>283</v>
       </c>
       <c r="C74" s="2">
         <v>69668</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D74" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F74" s="4" t="s">
-        <v>174</v>
+      <c r="F74" s="7" t="s">
+        <v>284</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="H74" s="6">
-        <v>44927</v>
+        <v>267</v>
+      </c>
+      <c r="H74" s="5">
+        <v>44091</v>
       </c>
       <c r="I74" s="2">
         <v>5</v>
@@ -4993,48 +5366,49 @@
       <c r="J74" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K74" s="6">
-        <v>39814</v>
-      </c>
-      <c r="L74" s="6">
+      <c r="K74" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L74" s="5">
         <v>33130</v>
       </c>
-      <c r="M74" s="6">
+      <c r="M74" s="5">
         <v>53601</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="O74" s="6">
+        <v>285</v>
+      </c>
+      <c r="O74" s="5">
         <v>46259</v>
       </c>
-      <c r="P74" s="3"/>
-      <c r="S74" s="3"/>
+      <c r="P74" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>175</v>
+        <v>286</v>
       </c>
       <c r="C75" s="2">
         <v>69996</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D75" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F75" s="4" t="s">
-        <v>174</v>
+      <c r="F75" s="7" t="s">
+        <v>284</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="H75" s="6">
-        <v>44927</v>
+        <v>267</v>
+      </c>
+      <c r="H75" s="5">
+        <v>44091</v>
       </c>
       <c r="I75" s="2">
         <v>5</v>
@@ -5042,48 +5416,49 @@
       <c r="J75" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K75" s="6">
+      <c r="K75" s="5">
         <v>42597</v>
       </c>
-      <c r="L75" s="6">
+      <c r="L75" s="5">
         <v>35783</v>
       </c>
-      <c r="M75" s="6">
+      <c r="M75" s="5">
         <v>56250</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="O75" s="6">
+        <v>287</v>
+      </c>
+      <c r="O75" s="5">
         <v>46259</v>
       </c>
-      <c r="P75" s="3"/>
-      <c r="S75" s="3"/>
+      <c r="P75" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A76" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>176</v>
+        <v>288</v>
       </c>
       <c r="C76" s="2">
         <v>55871</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="D76" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F76" s="4" t="s">
-        <v>177</v>
+      <c r="F76" s="7" t="s">
+        <v>289</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H76" s="8">
-        <v>45996</v>
+        <v>290</v>
+      </c>
+      <c r="H76" s="5">
+        <v>45550</v>
       </c>
       <c r="I76" s="2">
         <v>8</v>
@@ -5091,41 +5466,57 @@
       <c r="J76" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K76" s="6">
+      <c r="K76" s="5">
         <v>40163</v>
       </c>
-      <c r="L76" s="6">
+      <c r="L76" s="5">
         <v>33106</v>
       </c>
-      <c r="M76" s="6">
+      <c r="M76" s="5">
         <v>53571</v>
       </c>
-      <c r="P76" s="3"/>
-      <c r="S76" s="3"/>
+      <c r="N76" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="O76" s="5">
+        <v>47324</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q76" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="R76" s="5">
+        <v>47261</v>
+      </c>
+      <c r="S76" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="77" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>179</v>
+        <v>293</v>
       </c>
       <c r="C77" s="2">
         <v>53676</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D77" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F77" s="4" t="s">
-        <v>180</v>
+      <c r="F77" s="7" t="s">
+        <v>294</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H77" s="8">
+        <v>290</v>
+      </c>
+      <c r="H77" s="5">
         <v>45717</v>
       </c>
       <c r="I77" s="2">
@@ -5134,47 +5525,48 @@
       <c r="J77" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K77" s="6">
+      <c r="K77" s="5">
         <v>39814</v>
       </c>
-      <c r="L77" s="6">
+      <c r="L77" s="5">
         <v>31540</v>
       </c>
-      <c r="M77" s="6">
+      <c r="M77" s="5">
         <v>52018</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="O77" s="6">
+        <v>295</v>
+      </c>
+      <c r="O77" s="5">
         <v>46965</v>
       </c>
-      <c r="P77" s="3"/>
-      <c r="S77" s="3"/>
+      <c r="P77" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="78" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A78" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>181</v>
+        <v>296</v>
       </c>
       <c r="C78" s="2">
         <v>69684</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F78" s="4" t="s">
-        <v>182</v>
+      <c r="F78" s="7" t="s">
+        <v>297</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H78" s="8">
+        <v>290</v>
+      </c>
+      <c r="H78" s="5">
         <v>45108</v>
       </c>
       <c r="I78" s="2">
@@ -5183,48 +5575,49 @@
       <c r="J78" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K78" s="6">
+      <c r="K78" s="5">
         <v>42562</v>
       </c>
-      <c r="L78" s="6">
+      <c r="L78" s="5">
         <v>34162</v>
       </c>
-      <c r="M78" s="6">
+      <c r="M78" s="5">
         <v>54636</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="O78" s="6">
+        <v>298</v>
+      </c>
+      <c r="O78" s="5">
         <v>46673</v>
       </c>
-      <c r="P78" s="3"/>
-      <c r="S78" s="3"/>
+      <c r="P78" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A79" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>183</v>
+        <v>299</v>
       </c>
       <c r="C79" s="2">
         <v>71499</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F79" s="4" t="s">
-        <v>184</v>
+      <c r="F79" s="7" t="s">
+        <v>300</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H79" s="8">
-        <v>44927</v>
+        <v>290</v>
+      </c>
+      <c r="H79" s="5">
+        <v>43375</v>
       </c>
       <c r="I79" s="2">
         <v>5</v>
@@ -5232,42 +5625,49 @@
       <c r="J79" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K79" s="6">
-        <v>39814</v>
-      </c>
-      <c r="L79" s="6">
+      <c r="K79" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L79" s="5">
         <v>34781</v>
       </c>
-      <c r="M79" s="6">
+      <c r="M79" s="5">
         <v>55244</v>
       </c>
-      <c r="P79" s="3"/>
-      <c r="S79" s="3"/>
+      <c r="N79" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="O79" s="5">
+        <v>46246</v>
+      </c>
+      <c r="P79" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A80" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>185</v>
+        <v>302</v>
       </c>
       <c r="C80" s="2">
         <v>69139</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F80" s="4" t="s">
-        <v>184</v>
+      <c r="F80" s="7" t="s">
+        <v>300</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H80" s="8">
-        <v>44927</v>
+        <v>290</v>
+      </c>
+      <c r="H80" s="5">
+        <v>44091</v>
       </c>
       <c r="I80" s="2">
         <v>5</v>
@@ -5275,48 +5675,49 @@
       <c r="J80" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K80" s="6">
-        <v>39814</v>
-      </c>
-      <c r="L80" s="6">
+      <c r="K80" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L80" s="5">
         <v>34062</v>
       </c>
-      <c r="M80" s="6">
+      <c r="M80" s="5">
         <v>54544</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="O80" s="6">
+        <v>303</v>
+      </c>
+      <c r="O80" s="5">
         <v>46246</v>
       </c>
-      <c r="P80" s="3"/>
-      <c r="S80" s="3"/>
+      <c r="P80" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A81" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>186</v>
+        <v>304</v>
       </c>
       <c r="C81" s="2">
         <v>69178</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D81" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F81" s="4" t="s">
-        <v>187</v>
+      <c r="F81" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H81" s="8">
-        <v>44927</v>
+        <v>290</v>
+      </c>
+      <c r="H81" s="5">
+        <v>43319</v>
       </c>
       <c r="I81" s="2">
         <v>5</v>
@@ -5324,48 +5725,49 @@
       <c r="J81" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K81" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L81" s="6">
+      <c r="K81" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L81" s="5">
         <v>32032</v>
       </c>
-      <c r="M81" s="6">
-        <v>52505</v>
+      <c r="M81" s="5">
+        <v>52597</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="O81" s="6">
+        <v>306</v>
+      </c>
+      <c r="O81" s="5">
         <v>46246</v>
       </c>
-      <c r="P81" s="3"/>
-      <c r="S81" s="3"/>
+      <c r="P81" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A82" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>188</v>
+        <v>307</v>
       </c>
       <c r="C82" s="2">
         <v>71437</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D82" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F82" s="4" t="s">
-        <v>187</v>
+      <c r="F82" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H82" s="8">
-        <v>44927</v>
+        <v>290</v>
+      </c>
+      <c r="H82" s="5">
+        <v>43375</v>
       </c>
       <c r="I82" s="2">
         <v>5</v>
@@ -5373,47 +5775,48 @@
       <c r="J82" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K82" s="6">
+      <c r="K82" s="5">
         <v>43075</v>
       </c>
-      <c r="L82" s="6">
-        <v>34534</v>
-      </c>
-      <c r="M82" s="6">
+      <c r="L82" s="5">
+        <v>35885</v>
+      </c>
+      <c r="M82" s="5">
         <v>55001</v>
       </c>
       <c r="N82" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="O82" s="6">
+      <c r="O82" s="5">
         <v>46246</v>
       </c>
-      <c r="P82" s="3"/>
-      <c r="S82" s="3"/>
+      <c r="P82" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A83" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>189</v>
+        <v>309</v>
       </c>
       <c r="C83" s="2">
         <v>74675</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F83" s="4" t="s">
-        <v>187</v>
+      <c r="F83" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H83" s="8">
+        <v>290</v>
+      </c>
+      <c r="H83" s="5">
         <v>45176</v>
       </c>
       <c r="I83" s="2">
@@ -5422,47 +5825,48 @@
       <c r="J83" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K83" s="6">
+      <c r="K83" s="5">
         <v>44866</v>
       </c>
-      <c r="L83" s="6">
+      <c r="L83" s="5">
         <v>36831</v>
       </c>
-      <c r="M83" s="6">
+      <c r="M83" s="5">
         <v>57315</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="O83" s="6">
+        <v>310</v>
+      </c>
+      <c r="O83" s="5">
         <v>46916</v>
       </c>
-      <c r="P83" s="3"/>
-      <c r="S83" s="3"/>
+      <c r="P83" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A84" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>190</v>
+        <v>311</v>
       </c>
       <c r="C84" s="2">
         <v>49815</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D84" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F84" s="4" t="s">
-        <v>191</v>
+      <c r="F84" s="7" t="s">
+        <v>312</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H84" s="6">
+        <v>313</v>
+      </c>
+      <c r="H84" s="5">
         <v>45870</v>
       </c>
       <c r="I84" s="2">
@@ -5471,53 +5875,57 @@
       <c r="J84" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K84" s="6">
+      <c r="K84" s="5">
         <v>39387</v>
       </c>
-      <c r="L84" s="6">
+      <c r="L84" s="5">
         <v>31446</v>
       </c>
-      <c r="M84" s="6">
+      <c r="M84" s="5">
         <v>51926</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="O84" s="6">
+        <v>314</v>
+      </c>
+      <c r="O84" s="5">
         <v>47005</v>
       </c>
-      <c r="P84" s="3"/>
+      <c r="P84" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q84" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="R84" s="6">
+        <v>315</v>
+      </c>
+      <c r="R84" s="5">
         <v>47265</v>
       </c>
-      <c r="S84" s="3"/>
+      <c r="S84" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="85" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A85" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>193</v>
+        <v>316</v>
       </c>
       <c r="C85" s="2">
         <v>53847</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D85" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F85" s="4" t="s">
-        <v>194</v>
+      <c r="F85" s="7" t="s">
+        <v>317</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H85" s="6">
+        <v>313</v>
+      </c>
+      <c r="H85" s="5">
         <v>45717</v>
       </c>
       <c r="I85" s="2">
@@ -5526,41 +5934,48 @@
       <c r="J85" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K85" s="6">
-        <v>42597</v>
-      </c>
-      <c r="L85" s="6">
+      <c r="K85" s="5">
+        <v>39814</v>
+      </c>
+      <c r="L85" s="5">
         <v>32813</v>
       </c>
-      <c r="M85" s="6">
+      <c r="M85" s="5">
         <v>53297</v>
       </c>
-      <c r="P85" s="3"/>
-      <c r="S85" s="3"/>
+      <c r="N85" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="O85" s="5">
+        <v>46970</v>
+      </c>
+      <c r="P85" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="86" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A86" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>195</v>
+        <v>319</v>
       </c>
       <c r="C86" s="2">
         <v>56359</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="D86" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F86" s="4" t="s">
-        <v>196</v>
+      <c r="F86" s="7" t="s">
+        <v>320</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H86" s="6">
+        <v>313</v>
+      </c>
+      <c r="H86" s="5">
         <v>45519</v>
       </c>
       <c r="I86" s="2">
@@ -5569,47 +5984,48 @@
       <c r="J86" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K86" s="6">
+      <c r="K86" s="5">
         <v>40163</v>
       </c>
-      <c r="L86" s="6">
+      <c r="L86" s="5">
         <v>33172</v>
       </c>
-      <c r="M86" s="6">
+      <c r="M86" s="5">
         <v>53632</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="O86" s="6">
+        <v>321</v>
+      </c>
+      <c r="O86" s="5">
         <v>47005</v>
       </c>
-      <c r="P86" s="3"/>
-      <c r="S86" s="3"/>
+      <c r="P86" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A87" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>197</v>
+        <v>322</v>
       </c>
       <c r="C87" s="2">
         <v>56326</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D87" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F87" s="4" t="s">
-        <v>198</v>
+      <c r="F87" s="7" t="s">
+        <v>323</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H87" s="8">
+        <v>313</v>
+      </c>
+      <c r="H87" s="5">
         <v>45139</v>
       </c>
       <c r="I87" s="2">
@@ -5618,47 +6034,48 @@
       <c r="J87" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K87" s="6">
+      <c r="K87" s="5">
         <v>40163</v>
       </c>
-      <c r="L87" s="6">
+      <c r="L87" s="5">
         <v>31044</v>
       </c>
-      <c r="M87" s="6">
+      <c r="M87" s="5">
         <v>51502</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="O87" s="6">
+        <v>324</v>
+      </c>
+      <c r="O87" s="5">
         <v>46851</v>
       </c>
-      <c r="P87" s="3"/>
-      <c r="S87" s="3"/>
+      <c r="P87" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A88" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>199</v>
+        <v>325</v>
       </c>
       <c r="C88" s="2">
         <v>74488</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="D88" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F88" s="4" t="s">
-        <v>198</v>
+      <c r="F88" s="7" t="s">
+        <v>323</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H88" s="8">
+        <v>313</v>
+      </c>
+      <c r="H88" s="5">
         <v>45444</v>
       </c>
       <c r="I88" s="2">
@@ -5667,48 +6084,49 @@
       <c r="J88" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K88" s="6">
+      <c r="K88" s="5">
         <v>44816</v>
       </c>
-      <c r="L88" s="6">
+      <c r="L88" s="5">
         <v>37263</v>
       </c>
-      <c r="M88" s="6">
+      <c r="M88" s="5">
         <v>57742</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="O88" s="6">
+        <v>326</v>
+      </c>
+      <c r="O88" s="5">
         <v>47111</v>
       </c>
-      <c r="P88" s="3"/>
-      <c r="S88" s="3"/>
+      <c r="P88" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A89" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>200</v>
+        <v>327</v>
       </c>
       <c r="C89" s="2">
         <v>61470</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="D89" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F89" s="4" t="s">
-        <v>201</v>
+      <c r="F89" s="7" t="s">
+        <v>328</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H89" s="8">
-        <v>44927</v>
+        <v>313</v>
+      </c>
+      <c r="H89" s="5">
+        <v>43656</v>
       </c>
       <c r="I89" s="2">
         <v>5</v>
@@ -5716,48 +6134,49 @@
       <c r="J89" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K89" s="6">
+      <c r="K89" s="5">
         <v>40787</v>
       </c>
-      <c r="L89" s="6">
+      <c r="L89" s="5">
         <v>33922</v>
       </c>
-      <c r="M89" s="6">
+      <c r="M89" s="5">
         <v>54393</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="O89" s="6">
+        <v>329</v>
+      </c>
+      <c r="O89" s="5">
         <v>47054</v>
       </c>
-      <c r="P89" s="3"/>
-      <c r="S89" s="3"/>
+      <c r="P89" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A90" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>202</v>
+        <v>330</v>
       </c>
       <c r="C90" s="2">
         <v>71455</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="D90" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F90" s="4" t="s">
-        <v>201</v>
+      <c r="F90" s="7" t="s">
+        <v>328</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H90" s="6">
-        <v>44927</v>
+        <v>313</v>
+      </c>
+      <c r="H90" s="5">
+        <v>43329</v>
       </c>
       <c r="I90" s="2">
         <v>5</v>
@@ -5765,48 +6184,49 @@
       <c r="J90" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K90" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L90" s="6">
+      <c r="K90" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L90" s="5">
         <v>34185</v>
       </c>
-      <c r="M90" s="6">
+      <c r="M90" s="5">
         <v>54667</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="O90" s="6">
+        <v>331</v>
+      </c>
+      <c r="O90" s="5">
         <v>46407</v>
       </c>
-      <c r="P90" s="3"/>
-      <c r="S90" s="3"/>
+      <c r="P90" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A91" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>203</v>
+        <v>332</v>
       </c>
       <c r="C91" s="2">
         <v>69156</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D91" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F91" s="4" t="s">
-        <v>201</v>
+      <c r="F91" s="7" t="s">
+        <v>328</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H91" s="8">
-        <v>44927</v>
+        <v>313</v>
+      </c>
+      <c r="H91" s="5">
+        <v>43416</v>
       </c>
       <c r="I91" s="2">
         <v>5</v>
@@ -5814,41 +6234,48 @@
       <c r="J91" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K91" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L91" s="6">
+      <c r="K91" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L91" s="5">
         <v>34371</v>
       </c>
-      <c r="M91" s="6">
-        <v>54848</v>
-      </c>
-      <c r="P91" s="3"/>
-      <c r="S91" s="3"/>
+      <c r="M91" s="5">
+        <v>54970</v>
+      </c>
+      <c r="N91" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="O91" s="5">
+        <v>46305</v>
+      </c>
+      <c r="P91" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A92" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>204</v>
+        <v>334</v>
       </c>
       <c r="C92" s="2">
         <v>42082</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="D92" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F92" s="4" t="s">
-        <v>205</v>
+      <c r="F92" s="7" t="s">
+        <v>335</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H92" s="6">
+        <v>336</v>
+      </c>
+      <c r="H92" s="5">
         <v>45108</v>
       </c>
       <c r="I92" s="2">
@@ -5857,54 +6284,46 @@
       <c r="J92" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K92" s="6">
-        <v>34346</v>
-      </c>
-      <c r="L92" s="6">
+      <c r="K92" s="5">
+        <v>34669</v>
+      </c>
+      <c r="L92" s="5">
         <v>26222</v>
       </c>
-      <c r="M92" s="6">
+      <c r="M92" s="5">
         <v>46692</v>
       </c>
-      <c r="N92" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="O92" s="6">
-        <v>45766</v>
-      </c>
-      <c r="P92" s="3"/>
       <c r="Q92" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="R92" s="6">
+        <v>337</v>
+      </c>
+      <c r="R92" s="5">
         <v>47110</v>
       </c>
-      <c r="S92" s="3"/>
     </row>
     <row r="93" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A93" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>207</v>
+        <v>338</v>
       </c>
       <c r="C93" s="2">
         <v>53850</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="D93" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F93" s="4" t="s">
-        <v>208</v>
+      <c r="F93" s="7" t="s">
+        <v>339</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H93" s="6">
-        <v>44927</v>
+        <v>336</v>
+      </c>
+      <c r="H93" s="5">
+        <v>43952</v>
       </c>
       <c r="I93" s="2">
         <v>7</v>
@@ -5912,39 +6331,48 @@
       <c r="J93" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K93" s="6">
-        <v>42597</v>
-      </c>
-      <c r="L93" s="6">
+      <c r="K93" s="5">
+        <v>39814</v>
+      </c>
+      <c r="L93" s="5">
         <v>32817</v>
       </c>
-      <c r="M93" s="6">
+      <c r="M93" s="5">
         <v>53297</v>
+      </c>
+      <c r="N93" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="O93" s="5">
+        <v>47261</v>
+      </c>
+      <c r="P93" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="94" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A94" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>209</v>
+        <v>341</v>
       </c>
       <c r="C94" s="2">
         <v>53859</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F94" s="4" t="s">
-        <v>210</v>
+      <c r="F94" s="7" t="s">
+        <v>342</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H94" s="6">
+        <v>336</v>
+      </c>
+      <c r="H94" s="5">
         <v>45017</v>
       </c>
       <c r="I94" s="2">
@@ -5953,45 +6381,48 @@
       <c r="J94" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K94" s="6">
+      <c r="K94" s="5">
         <v>39814</v>
       </c>
-      <c r="L94" s="6">
+      <c r="L94" s="5">
         <v>32839</v>
       </c>
-      <c r="M94" s="6">
+      <c r="M94" s="5">
         <v>53297</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="O94" s="6">
+        <v>343</v>
+      </c>
+      <c r="O94" s="5">
         <v>46953</v>
+      </c>
+      <c r="P94" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A95" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>211</v>
+        <v>344</v>
       </c>
       <c r="C95" s="2">
         <v>74490</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="D95" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F95" s="4" t="s">
-        <v>212</v>
+      <c r="F95" s="7" t="s">
+        <v>345</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H95" s="6">
+        <v>336</v>
+      </c>
+      <c r="H95" s="5">
         <v>45748</v>
       </c>
       <c r="I95" s="2">
@@ -6000,46 +6431,49 @@
       <c r="J95" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K95" s="6">
+      <c r="K95" s="5">
         <v>44816</v>
       </c>
-      <c r="L95" s="6">
+      <c r="L95" s="5">
         <v>37576</v>
       </c>
-      <c r="M95" s="6">
+      <c r="M95" s="5">
         <v>58045</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="O95" s="6">
+        <v>346</v>
+      </c>
+      <c r="O95" s="5">
         <v>46950</v>
+      </c>
+      <c r="P95" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A96" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>213</v>
+        <v>347</v>
       </c>
       <c r="C96" s="2">
         <v>56292</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F96" s="4" t="s">
-        <v>212</v>
+      <c r="F96" s="7" t="s">
+        <v>345</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H96" s="6">
-        <v>44927</v>
+        <v>336</v>
+      </c>
+      <c r="H96" s="5">
+        <v>44091</v>
       </c>
       <c r="I96" s="2">
         <v>5</v>
@@ -6047,45 +6481,48 @@
       <c r="J96" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K96" s="6">
+      <c r="K96" s="5">
         <v>40163</v>
       </c>
-      <c r="L96" s="6">
+      <c r="L96" s="5">
         <v>31609</v>
       </c>
-      <c r="M96" s="6">
+      <c r="M96" s="5">
         <v>52079</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="O96" s="6">
+        <v>348</v>
+      </c>
+      <c r="O96" s="5">
         <v>46937</v>
       </c>
-    </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P96" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A97" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>214</v>
+        <v>349</v>
       </c>
       <c r="C97" s="2">
         <v>74805</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="D97" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F97" s="4" t="s">
-        <v>212</v>
+      <c r="F97" s="7" t="s">
+        <v>345</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H97" s="6">
+        <v>336</v>
+      </c>
+      <c r="H97" s="5">
         <v>45839</v>
       </c>
       <c r="I97" s="2">
@@ -6094,40 +6531,40 @@
       <c r="J97" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K97" s="6">
+      <c r="K97" s="5">
         <v>44866</v>
       </c>
-      <c r="L97" s="6">
+      <c r="L97" s="5">
         <v>37735</v>
       </c>
-      <c r="M97" s="6">
+      <c r="M97" s="5">
         <v>58196</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A98" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>215</v>
+        <v>350</v>
       </c>
       <c r="C98" s="2">
         <v>62060</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="D98" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F98" s="4" t="s">
-        <v>216</v>
+      <c r="F98" s="7" t="s">
+        <v>351</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H98" s="6">
-        <v>44927</v>
+        <v>336</v>
+      </c>
+      <c r="H98" s="5">
+        <v>44091</v>
       </c>
       <c r="I98" s="2">
         <v>5</v>
@@ -6135,45 +6572,48 @@
       <c r="J98" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K98" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L98" s="6">
+      <c r="K98" s="5">
+        <v>41153</v>
+      </c>
+      <c r="L98" s="5">
         <v>31724</v>
       </c>
-      <c r="M98" s="6">
+      <c r="M98" s="5">
         <v>52201</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="O98" s="6">
+        <v>352</v>
+      </c>
+      <c r="O98" s="5">
         <v>46937</v>
       </c>
-    </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P98" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A99" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>217</v>
+        <v>353</v>
       </c>
       <c r="C99" s="2">
         <v>75388</v>
       </c>
-      <c r="D99" s="3" t="s">
+      <c r="D99" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F99" s="4" t="s">
-        <v>216</v>
+      <c r="F99" s="7" t="s">
+        <v>351</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H99" s="6">
+        <v>336</v>
+      </c>
+      <c r="H99" s="5">
         <v>45519</v>
       </c>
       <c r="I99" s="2">
@@ -6182,46 +6622,49 @@
       <c r="J99" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K99" s="6">
+      <c r="K99" s="5">
         <v>44958</v>
       </c>
-      <c r="L99" s="6">
+      <c r="L99" s="5">
         <v>37707</v>
       </c>
-      <c r="M99" s="6">
+      <c r="M99" s="5">
         <v>58166</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="O99" s="6">
+        <v>354</v>
+      </c>
+      <c r="O99" s="5">
         <v>47110</v>
       </c>
-    </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P99" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A100" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>218</v>
+        <v>355</v>
       </c>
       <c r="C100" s="2">
         <v>69059</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D100" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F100" s="4" t="s">
-        <v>216</v>
+      <c r="F100" s="7" t="s">
+        <v>351</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H100" s="6">
-        <v>44927</v>
+        <v>336</v>
+      </c>
+      <c r="H100" s="5">
+        <v>43040</v>
       </c>
       <c r="I100" s="2">
         <v>5</v>
@@ -6229,46 +6672,49 @@
       <c r="J100" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K100" s="6">
+      <c r="K100" s="5">
         <v>42562</v>
       </c>
-      <c r="L100" s="6">
+      <c r="L100" s="5">
         <v>34700</v>
       </c>
-      <c r="M100" s="6">
+      <c r="M100" s="5">
         <v>55185</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="O100" s="6">
+        <v>356</v>
+      </c>
+      <c r="O100" s="5">
         <v>46407</v>
       </c>
-    </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P100" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A101" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>219</v>
+        <v>357</v>
       </c>
       <c r="C101" s="2">
         <v>50257</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F101" s="4" t="s">
-        <v>220</v>
+      <c r="F101" s="7" t="s">
+        <v>358</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="H101" s="6">
-        <v>44927</v>
+        <v>359</v>
+      </c>
+      <c r="H101" s="5">
+        <v>44883</v>
       </c>
       <c r="I101" s="2">
         <v>8</v>
@@ -6276,51 +6722,48 @@
       <c r="J101" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K101" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L101" s="6">
+      <c r="K101" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L101" s="5">
         <v>32387</v>
       </c>
-      <c r="M101" s="6">
+      <c r="M101" s="5">
         <v>52871</v>
       </c>
-      <c r="N101" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="O101" s="6">
+      <c r="Q101" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="R101" s="5">
         <v>47054</v>
       </c>
-      <c r="Q101" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="R101" s="6">
-        <v>47054</v>
-      </c>
-    </row>
-    <row r="102" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S101" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A102" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>222</v>
+        <v>361</v>
       </c>
       <c r="C102" s="2">
         <v>53705</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="D102" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F102" s="4" t="s">
-        <v>223</v>
+      <c r="F102" s="7" t="s">
+        <v>362</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="H102" s="6">
+        <v>359</v>
+      </c>
+      <c r="H102" s="5">
         <v>45717</v>
       </c>
       <c r="I102" s="2">
@@ -6329,45 +6772,48 @@
       <c r="J102" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K102" s="6">
+      <c r="K102" s="5">
         <v>39814</v>
       </c>
-      <c r="L102" s="6">
+      <c r="L102" s="5">
         <v>32268</v>
       </c>
-      <c r="M102" s="6">
+      <c r="M102" s="5">
         <v>52749</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="O102" s="6">
+        <v>363</v>
+      </c>
+      <c r="O102" s="5">
         <v>46950</v>
       </c>
-    </row>
-    <row r="103" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P102" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A103" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>224</v>
+        <v>364</v>
       </c>
       <c r="C103" s="2">
         <v>56307</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="D103" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F103" s="4" t="s">
-        <v>225</v>
+      <c r="F103" s="7" t="s">
+        <v>365</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="H103" s="6">
+        <v>359</v>
+      </c>
+      <c r="H103" s="5">
         <v>45519</v>
       </c>
       <c r="I103" s="2">
@@ -6376,45 +6822,48 @@
       <c r="J103" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K103" s="6">
+      <c r="K103" s="5">
         <v>40163</v>
       </c>
-      <c r="L103" s="6">
+      <c r="L103" s="5">
         <v>31944</v>
       </c>
-      <c r="M103" s="6">
+      <c r="M103" s="5">
         <v>52413</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="O103" s="6">
+        <v>366</v>
+      </c>
+      <c r="O103" s="5">
         <v>47054</v>
       </c>
-    </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P103" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A104" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>226</v>
+        <v>367</v>
       </c>
       <c r="C104" s="2">
         <v>71442</v>
       </c>
-      <c r="D104" s="3" t="s">
+      <c r="D104" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F104" s="4" t="s">
-        <v>227</v>
+      <c r="F104" s="7" t="s">
+        <v>368</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="H104" s="6">
+        <v>359</v>
+      </c>
+      <c r="H104" s="5">
         <v>45748</v>
       </c>
       <c r="I104" s="2">
@@ -6423,46 +6872,49 @@
       <c r="J104" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K104" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L104" s="6">
+      <c r="K104" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L104" s="5">
         <v>34837</v>
       </c>
-      <c r="M104" s="6">
+      <c r="M104" s="5">
         <v>55305</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="O104" s="6">
+        <v>369</v>
+      </c>
+      <c r="O104" s="5">
         <v>46433</v>
       </c>
-    </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P104" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A105" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>228</v>
+        <v>370</v>
       </c>
       <c r="C105" s="2">
         <v>69995</v>
       </c>
-      <c r="D105" s="3" t="s">
+      <c r="D105" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F105" s="4" t="s">
-        <v>227</v>
+      <c r="F105" s="7" t="s">
+        <v>368</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="H105" s="6">
-        <v>44927</v>
+        <v>359</v>
+      </c>
+      <c r="H105" s="5">
+        <v>43747</v>
       </c>
       <c r="I105" s="2">
         <v>5</v>
@@ -6470,45 +6922,48 @@
       <c r="J105" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K105" s="6">
-        <v>40163</v>
-      </c>
-      <c r="L105" s="6">
+      <c r="K105" s="5">
+        <v>42597</v>
+      </c>
+      <c r="L105" s="5">
         <v>34177</v>
       </c>
-      <c r="M105" s="6">
+      <c r="M105" s="5">
         <v>54636</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="O105" s="6">
+        <v>371</v>
+      </c>
+      <c r="O105" s="5">
         <v>46305</v>
       </c>
-    </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P105" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A106" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>229</v>
+        <v>372</v>
       </c>
       <c r="C106" s="2">
         <v>74584</v>
       </c>
-      <c r="D106" s="3" t="s">
+      <c r="D106" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F106" s="4" t="s">
-        <v>227</v>
+      <c r="F106" s="7" t="s">
+        <v>368</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="H106" s="6">
+        <v>359</v>
+      </c>
+      <c r="H106" s="5">
         <v>45839</v>
       </c>
       <c r="I106" s="2">
@@ -6517,46 +6972,49 @@
       <c r="J106" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K106" s="6">
+      <c r="K106" s="5">
         <v>44866</v>
       </c>
-      <c r="L106" s="6">
+      <c r="L106" s="5">
         <v>37445</v>
       </c>
-      <c r="M106" s="6">
+      <c r="M106" s="5">
         <v>57923</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="O106" s="6">
+        <v>373</v>
+      </c>
+      <c r="O106" s="5">
         <v>47114</v>
       </c>
-    </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P106" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A107" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>230</v>
+        <v>374</v>
       </c>
       <c r="C107" s="2">
         <v>69998</v>
       </c>
-      <c r="D107" s="3" t="s">
+      <c r="D107" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F107" s="4" t="s">
-        <v>231</v>
+      <c r="F107" s="7" t="s">
+        <v>375</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="H107" s="6">
-        <v>44927</v>
+        <v>359</v>
+      </c>
+      <c r="H107" s="5">
+        <v>44441</v>
       </c>
       <c r="I107" s="2">
         <v>5</v>
@@ -6564,46 +7022,49 @@
       <c r="J107" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K107" s="6">
+      <c r="K107" s="5">
         <v>42597</v>
       </c>
-      <c r="L107" s="6">
+      <c r="L107" s="5">
         <v>33521</v>
       </c>
-      <c r="M107" s="6">
+      <c r="M107" s="5">
         <v>53997</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="O107" s="6">
+        <v>376</v>
+      </c>
+      <c r="O107" s="5">
         <v>46305</v>
       </c>
-    </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P107" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A108" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>232</v>
+        <v>377</v>
       </c>
       <c r="C108" s="2">
         <v>61485</v>
       </c>
-      <c r="D108" s="3" t="s">
+      <c r="D108" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F108" s="4" t="s">
-        <v>231</v>
+      <c r="F108" s="7" t="s">
+        <v>375</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="H108" s="6">
-        <v>44927</v>
+        <v>359</v>
+      </c>
+      <c r="H108" s="5">
+        <v>42583</v>
       </c>
       <c r="I108" s="2">
         <v>5</v>
@@ -6611,39 +7072,48 @@
       <c r="J108" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K108" s="6">
-        <v>42439</v>
-      </c>
-      <c r="L108" s="6">
+      <c r="K108" s="5">
+        <v>40787</v>
+      </c>
+      <c r="L108" s="5">
         <v>34173</v>
       </c>
-      <c r="M108" s="6">
+      <c r="M108" s="5">
         <v>54636</v>
       </c>
-    </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="N108" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="O108" s="5">
+        <v>46861</v>
+      </c>
+      <c r="P108" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A109" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>233</v>
+        <v>379</v>
       </c>
       <c r="C109" s="2">
         <v>61468</v>
       </c>
-      <c r="D109" s="3" t="s">
+      <c r="D109" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F109" s="4" t="s">
-        <v>231</v>
+      <c r="F109" s="7" t="s">
+        <v>375</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="H109" s="6">
+        <v>359</v>
+      </c>
+      <c r="H109" s="5">
         <v>45139</v>
       </c>
       <c r="I109" s="2">
@@ -6652,46 +7122,49 @@
       <c r="J109" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K109" s="6">
-        <v>40552</v>
-      </c>
-      <c r="L109" s="6">
+      <c r="K109" s="5">
+        <v>40787</v>
+      </c>
+      <c r="L109" s="5">
         <v>33868</v>
       </c>
-      <c r="M109" s="6">
+      <c r="M109" s="5">
         <v>54332</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="O109" s="6">
+        <v>380</v>
+      </c>
+      <c r="O109" s="5">
         <v>46950</v>
       </c>
-    </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="P109" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A110" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>234</v>
+        <v>381</v>
       </c>
       <c r="C110" s="2">
         <v>50296</v>
       </c>
-      <c r="D110" s="3" t="s">
+      <c r="D110" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F110" s="4" t="s">
-        <v>235</v>
+      <c r="F110" s="7" t="s">
+        <v>382</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="H110" s="6">
-        <v>44927</v>
+        <v>383</v>
+      </c>
+      <c r="H110" s="5">
+        <v>44883</v>
       </c>
       <c r="I110" s="2">
         <v>8</v>
@@ -6699,51 +7172,57 @@
       <c r="J110" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K110" s="6">
-        <v>39814</v>
-      </c>
-      <c r="L110" s="6">
+      <c r="K110" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L110" s="5">
         <v>32473</v>
       </c>
-      <c r="M110" s="6">
-        <v>52932</v>
+      <c r="M110" s="5">
+        <v>52902</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="O110" s="6">
+        <v>384</v>
+      </c>
+      <c r="O110" s="5">
         <v>47054</v>
       </c>
+      <c r="P110" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q110" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="R110" s="6">
+        <v>385</v>
+      </c>
+      <c r="R110" s="5">
         <v>47005</v>
       </c>
-    </row>
-    <row r="111" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S110" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A111" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>237</v>
+        <v>386</v>
       </c>
       <c r="C111" s="2">
         <v>53845</v>
       </c>
-      <c r="D111" s="3" t="s">
+      <c r="D111" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F111" s="4" t="s">
-        <v>238</v>
+      <c r="F111" s="7" t="s">
+        <v>387</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="H111" s="6">
+        <v>383</v>
+      </c>
+      <c r="H111" s="5">
         <v>45717</v>
       </c>
       <c r="I111" s="2">
@@ -6752,40 +7231,49 @@
       <c r="J111" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K111" s="6">
-        <v>40163</v>
-      </c>
-      <c r="L111" s="6">
+      <c r="K111" s="5">
+        <v>39814</v>
+      </c>
+      <c r="L111" s="5">
         <v>32806</v>
       </c>
-      <c r="M111" s="6">
+      <c r="M111" s="5">
         <v>53267</v>
       </c>
-    </row>
-    <row r="112" spans="1:18" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="N111" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="O111" s="5">
+        <v>47054</v>
+      </c>
+      <c r="P111" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A112" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>239</v>
+        <v>389</v>
       </c>
       <c r="C112" s="2">
         <v>53701</v>
       </c>
-      <c r="D112" s="3" t="s">
+      <c r="D112" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F112" s="4" t="s">
-        <v>240</v>
+      <c r="F112" s="7" t="s">
+        <v>390</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="H112" s="6">
-        <v>44927</v>
+        <v>383</v>
+      </c>
+      <c r="H112" s="5">
+        <v>44883</v>
       </c>
       <c r="I112" s="2">
         <v>7</v>
@@ -6793,46 +7281,49 @@
       <c r="J112" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K112" s="6">
+      <c r="K112" s="5">
         <v>39814</v>
       </c>
-      <c r="L112" s="6">
+      <c r="L112" s="5">
         <v>32214</v>
       </c>
-      <c r="M112" s="6">
+      <c r="M112" s="5">
         <v>52688</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="O112" s="6">
+        <v>391</v>
+      </c>
+      <c r="O112" s="5">
         <v>47005</v>
       </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P112" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A113" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>241</v>
+        <v>392</v>
       </c>
       <c r="C113" s="2">
         <v>70800</v>
       </c>
-      <c r="D113" s="3" t="s">
+      <c r="D113" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F113" s="4" t="s">
-        <v>242</v>
+      <c r="F113" s="7" t="s">
+        <v>393</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="H113" s="6">
-        <v>44927</v>
+        <v>383</v>
+      </c>
+      <c r="H113" s="5">
+        <v>44091</v>
       </c>
       <c r="I113" s="2">
         <v>5</v>
@@ -6840,45 +7331,48 @@
       <c r="J113" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K113" s="6">
+      <c r="K113" s="5">
         <v>42725</v>
       </c>
-      <c r="L113" s="6">
+      <c r="L113" s="5">
         <v>34496</v>
       </c>
-      <c r="M113" s="6">
+      <c r="M113" s="5">
         <v>54970</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="O113" s="6">
+        <v>394</v>
+      </c>
+      <c r="O113" s="5">
         <v>46263</v>
       </c>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P113" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A114" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>243</v>
+        <v>395</v>
       </c>
       <c r="C114" s="2">
         <v>69163</v>
       </c>
-      <c r="D114" s="3" t="s">
+      <c r="D114" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F114" s="4" t="s">
-        <v>242</v>
+      <c r="F114" s="7" t="s">
+        <v>393</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="H114" s="6">
+        <v>383</v>
+      </c>
+      <c r="H114" s="5">
         <v>45139</v>
       </c>
       <c r="I114" s="2">
@@ -6887,45 +7381,48 @@
       <c r="J114" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K114" s="6">
-        <v>40552</v>
-      </c>
-      <c r="L114" s="6">
+      <c r="K114" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L114" s="5">
         <v>33609</v>
       </c>
-      <c r="M114" s="6">
+      <c r="M114" s="5">
         <v>54089</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="O114" s="6">
+        <v>396</v>
+      </c>
+      <c r="O114" s="5">
         <v>46305</v>
       </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P114" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A115" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>244</v>
+        <v>397</v>
       </c>
       <c r="C115" s="2">
         <v>70108</v>
       </c>
-      <c r="D115" s="3" t="s">
+      <c r="D115" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F115" s="4" t="s">
-        <v>242</v>
+      <c r="F115" s="7" t="s">
+        <v>393</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="H115" s="6">
+        <v>383</v>
+      </c>
+      <c r="H115" s="5">
         <v>45748</v>
       </c>
       <c r="I115" s="2">
@@ -6934,46 +7431,49 @@
       <c r="J115" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K115" s="6">
+      <c r="K115" s="5">
         <v>42597</v>
       </c>
-      <c r="L115" s="6">
+      <c r="L115" s="5">
         <v>32801</v>
       </c>
-      <c r="M115" s="6">
+      <c r="M115" s="5">
         <v>53267</v>
       </c>
       <c r="N115" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="O115" s="6">
+        <v>398</v>
+      </c>
+      <c r="O115" s="5">
         <v>46305</v>
       </c>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P115" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A116" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>245</v>
+        <v>399</v>
       </c>
       <c r="C116" s="2">
         <v>69090</v>
       </c>
-      <c r="D116" s="3" t="s">
+      <c r="D116" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F116" s="4" t="s">
-        <v>246</v>
+      <c r="F116" s="7" t="s">
+        <v>400</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="H116" s="6">
-        <v>44927</v>
+        <v>383</v>
+      </c>
+      <c r="H116" s="5">
+        <v>44091</v>
       </c>
       <c r="I116" s="2">
         <v>5</v>
@@ -6981,40 +7481,49 @@
       <c r="J116" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K116" s="6">
-        <v>42597</v>
-      </c>
-      <c r="L116" s="6">
+      <c r="K116" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L116" s="5">
         <v>33662</v>
       </c>
-      <c r="M116" s="6">
+      <c r="M116" s="5">
         <v>54118</v>
       </c>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="N116" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="O116" s="5">
+        <v>46446</v>
+      </c>
+      <c r="P116" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A117" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>247</v>
+        <v>402</v>
       </c>
       <c r="C117" s="2">
         <v>56289</v>
       </c>
-      <c r="D117" s="3" t="s">
+      <c r="D117" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F117" s="4" t="s">
-        <v>246</v>
+      <c r="F117" s="7" t="s">
+        <v>400</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="H117" s="6">
-        <v>44927</v>
+        <v>383</v>
+      </c>
+      <c r="H117" s="5">
+        <v>43668</v>
       </c>
       <c r="I117" s="2">
         <v>5</v>
@@ -7022,46 +7531,150 @@
       <c r="J117" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K117" s="6">
+      <c r="K117" s="5">
         <v>40163</v>
       </c>
-      <c r="L117" s="6">
+      <c r="L117" s="5">
         <v>32575</v>
       </c>
-      <c r="M117" s="6">
+      <c r="M117" s="5">
         <v>53053</v>
       </c>
       <c r="N117" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="O117" s="6">
+        <v>403</v>
+      </c>
+      <c r="O117" s="5">
         <v>46916</v>
       </c>
-    </row>
+      <c r="P117" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="129" x14ac:dyDescent="0.45"/>
+    <row r="130" x14ac:dyDescent="0.45"/>
+    <row r="131" x14ac:dyDescent="0.45"/>
+    <row r="132" x14ac:dyDescent="0.45"/>
+    <row r="133" x14ac:dyDescent="0.45"/>
+    <row r="134" x14ac:dyDescent="0.45"/>
+    <row r="135" x14ac:dyDescent="0.45"/>
+    <row r="136" x14ac:dyDescent="0.45"/>
+    <row r="137" x14ac:dyDescent="0.45"/>
+    <row r="138" x14ac:dyDescent="0.45"/>
+    <row r="139" x14ac:dyDescent="0.45"/>
+    <row r="140" x14ac:dyDescent="0.45"/>
+    <row r="141" x14ac:dyDescent="0.45"/>
+    <row r="142" x14ac:dyDescent="0.45"/>
+    <row r="143" x14ac:dyDescent="0.45"/>
+    <row r="144" x14ac:dyDescent="0.45"/>
+    <row r="145" x14ac:dyDescent="0.45"/>
+    <row r="146" x14ac:dyDescent="0.45"/>
+    <row r="147" x14ac:dyDescent="0.45"/>
+    <row r="148" x14ac:dyDescent="0.45"/>
+    <row r="149" x14ac:dyDescent="0.45"/>
+    <row r="150" x14ac:dyDescent="0.45"/>
+    <row r="151" x14ac:dyDescent="0.45"/>
+    <row r="152" x14ac:dyDescent="0.45"/>
+    <row r="153" x14ac:dyDescent="0.45"/>
+    <row r="154" x14ac:dyDescent="0.45"/>
+    <row r="155" x14ac:dyDescent="0.45"/>
+    <row r="156" x14ac:dyDescent="0.45"/>
+    <row r="157" x14ac:dyDescent="0.45"/>
+    <row r="158" x14ac:dyDescent="0.45"/>
+    <row r="159" x14ac:dyDescent="0.45"/>
+    <row r="160" x14ac:dyDescent="0.45"/>
+    <row r="161" x14ac:dyDescent="0.45"/>
+    <row r="162" x14ac:dyDescent="0.45"/>
+    <row r="163" x14ac:dyDescent="0.45"/>
+    <row r="164" x14ac:dyDescent="0.45"/>
+    <row r="165" x14ac:dyDescent="0.45"/>
+    <row r="166" x14ac:dyDescent="0.45"/>
+    <row r="167" x14ac:dyDescent="0.45"/>
+    <row r="168" x14ac:dyDescent="0.45"/>
+    <row r="169" x14ac:dyDescent="0.45"/>
+    <row r="170" x14ac:dyDescent="0.45"/>
+    <row r="171" x14ac:dyDescent="0.45"/>
+    <row r="172" x14ac:dyDescent="0.45"/>
+    <row r="173" x14ac:dyDescent="0.45"/>
+    <row r="174" x14ac:dyDescent="0.45"/>
+    <row r="175" x14ac:dyDescent="0.45"/>
+    <row r="176" x14ac:dyDescent="0.45"/>
+    <row r="177" x14ac:dyDescent="0.45"/>
+    <row r="178" x14ac:dyDescent="0.45"/>
+    <row r="179" x14ac:dyDescent="0.45"/>
+    <row r="180" x14ac:dyDescent="0.45"/>
+    <row r="181" x14ac:dyDescent="0.45"/>
+    <row r="182" x14ac:dyDescent="0.45"/>
+    <row r="183" x14ac:dyDescent="0.45"/>
+    <row r="184" x14ac:dyDescent="0.45"/>
+    <row r="185" x14ac:dyDescent="0.45"/>
+    <row r="186" x14ac:dyDescent="0.45"/>
+    <row r="187" x14ac:dyDescent="0.45"/>
+    <row r="188" x14ac:dyDescent="0.45"/>
+    <row r="189" x14ac:dyDescent="0.45"/>
+    <row r="190" x14ac:dyDescent="0.45"/>
+    <row r="191" x14ac:dyDescent="0.45"/>
+    <row r="192" x14ac:dyDescent="0.45"/>
+    <row r="193" x14ac:dyDescent="0.45"/>
+    <row r="194" x14ac:dyDescent="0.45"/>
+    <row r="195" x14ac:dyDescent="0.45"/>
+    <row r="196" x14ac:dyDescent="0.45"/>
+    <row r="197" x14ac:dyDescent="0.45"/>
+    <row r="198" x14ac:dyDescent="0.45"/>
+    <row r="199" x14ac:dyDescent="0.45"/>
+    <row r="200" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <autoFilter ref="A1:T117" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T199" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$A$1:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D994</xm:sqref>
+          <xm:sqref>D2:D986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$B$1:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J994</xm:sqref>
+          <xm:sqref>J2:J986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$C$1:$C$15</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I994</xm:sqref>
+          <xm:sqref>I2:I986</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{354EFE19-C43E-4A2D-83B1-FD15C013476E}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$D:$D</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G200</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9DE71029-D453-4F4E-B557-CC5A72AEA9EB}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$E:$E</xm:f>
+          </x14:formula1>
+          <xm:sqref>P2:P200 S2:S200</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{262E53F9-7911-451D-88C9-1E420930ED84}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$F:$F</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E200</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7071,130 +7684,297 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.59765625" customWidth="1"/>
+    <col min="1" max="1" width="16.73046875" style="8" customWidth="1"/>
+    <col min="2" max="3" width="9.06640625" style="8"/>
+    <col min="4" max="4" width="14.46484375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="49.53125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C1">
+      <c r="C1" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="D1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="D2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="D3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4">
+      <c r="B4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="8">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+      <c r="D4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="8">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+      <c r="D5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="8">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+      <c r="D6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+      <c r="D7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="8">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="D8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="8">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C10">
+      <c r="D9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C10" s="8">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C11">
+      <c r="D10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C11" s="8">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C12">
+      <c r="D11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C12" s="8">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C13">
+      <c r="D12" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C13" s="8">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C14">
+      <c r="D13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C14" s="8">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C15">
+      <c r="D14" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C15" s="8">
         <v>18</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="D16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="D17" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F18" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F19" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F20" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F21" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F22" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F23" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F24" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F25" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F26" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
